--- a/data/output/workbook/2026-07-02.xlsx
+++ b/data/output/workbook/2026-07-02.xlsx
@@ -247,13 +247,13 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -431,7 +431,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10544175"/>
+    <ext cx="10125075" cy="10096500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10506075"/>
+    <ext cx="10125075" cy="10696575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02 02:40</t>
+          <t>2026-07-02 06:01</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,891 +1175,887 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="29" t="inlineStr">
+        <is>
+          <t>Miami Marlins offense vs Colorado Rockies defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B65" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C65" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D65" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E65" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F65" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G65" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H65" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I65" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J65" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K65" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L65" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M65" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N65" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O65" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P65" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q65" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="n">
+        <v>4.526</v>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="D66" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F66" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G66" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H66" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J66" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="L66" s="32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M66" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N66" s="32" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="O66" s="32" t="n">
+        <v>6.567</v>
+      </c>
+      <c r="P66" s="32" t="n">
+        <v>5.697</v>
+      </c>
+      <c r="Q66" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
-        <is>
-          <t>Miami Marlins offense vs Colorado Rockies defense</t>
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>8.286</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O67" s="32" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="P67" s="32" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B68" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C68" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D68" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E68" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F68" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G68" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H68" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I68" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J68" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K68" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L68" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M68" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N68" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O68" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P68" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q68" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>4.547</v>
+        <v>7.816</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G69" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="n">
         <v>6.8</v>
       </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>6.6</v>
-      </c>
       <c r="P69" s="32" t="n">
-        <v>5.733</v>
+        <v>7.28</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H70" s="36" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="29" t="inlineStr">
+        <is>
+          <t>Colorado Rockies offense vs Miami Marlins defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B73" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C73" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D73" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E73" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F73" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G73" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H73" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I73" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J73" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K73" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L73" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M73" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N73" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O73" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P73" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q73" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>4.658</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>4.184</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>Hits/G</t>
         </is>
       </c>
-      <c r="B70" s="32" t="n">
-        <v>8.286</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>11.833</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
+      <c r="B75" s="32" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>7.694</v>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
         <is>
           <t>HR/G</t>
         </is>
       </c>
-      <c r="B71" s="32" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q71" s="35" t="inlineStr">
+      <c r="B76" s="32" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
         <is>
           <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>7.816</v>
-      </c>
-      <c r="C72" s="32" t="n">
-        <v>8.833</v>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="Q72" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>0.534</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J73" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
-        <is>
-          <t>Colorado Rockies offense vs Miami Marlins defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B76" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C76" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D76" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E76" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F76" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G76" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H76" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I76" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J76" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K76" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L76" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M76" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N76" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O76" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P76" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q76" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>4.64</v>
+        <v>8.92</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>5.633</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>6.067</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>3.15</v>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>3.567</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>4.16</v>
+        <v>8.531000000000001</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>8.32</v>
+        <v>0.467</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.5</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>0.4</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>7.667</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>7.694</v>
+        <v>0.635</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B79" s="32" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q79" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B80" s="32" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="C80" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="P80" s="32" t="n">
-        <v>8.531000000000001</v>
-      </c>
-      <c r="Q80" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="C81" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G81" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L81" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O81" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -2196,55 +2192,55 @@
         </is>
       </c>
       <c r="B68" s="32" t="n">
-        <v>4.986</v>
+        <v>4.932</v>
       </c>
       <c r="C68" s="32" t="n">
-        <v>5.6</v>
+        <v>5.133</v>
       </c>
       <c r="D68" s="32" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="E68" s="32" t="n">
-        <v>5.467</v>
+        <v>5.133</v>
       </c>
       <c r="F68" s="32" t="n">
         <v>6.1</v>
       </c>
       <c r="G68" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="H68" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
+        <v>4.8</v>
+      </c>
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t>13th</t>
         </is>
       </c>
       <c r="I68" s="32" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J68" s="34" t="inlineStr">
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J68" s="36" t="inlineStr">
         <is>
           <t>16th</t>
         </is>
       </c>
       <c r="K68" s="32" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L68" s="32" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="M68" s="32" t="n">
-        <v>3.867</v>
+        <v>4.067</v>
       </c>
       <c r="N68" s="32" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O68" s="32" t="n">
-        <v>4.333</v>
+        <v>4.267</v>
       </c>
       <c r="P68" s="32" t="n">
-        <v>4.132</v>
+        <v>4.13</v>
       </c>
       <c r="Q68" s="35" t="inlineStr">
         <is>
@@ -2262,7 +2258,7 @@
         <v>7.792</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>10</v>
+        <v>8.667</v>
       </c>
       <c r="D69" s="32" t="inlineStr">
         <is>
@@ -2316,7 +2312,7 @@
         </is>
       </c>
       <c r="O69" s="32" t="n">
-        <v>9.667</v>
+        <v>9.4</v>
       </c>
       <c r="P69" s="32" t="n">
         <v>7.939</v>
@@ -2337,7 +2333,7 @@
         <v>1.354</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>1.429</v>
+        <v>1.333</v>
       </c>
       <c r="D70" s="32" t="inlineStr">
         <is>
@@ -2416,7 +2412,7 @@
         <v>9.208</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>8.143000000000001</v>
+        <v>8.167</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -2470,7 +2466,7 @@
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>8.667</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P71" s="32" t="n">
         <v>9.388</v>
@@ -2488,26 +2484,26 @@
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>0.592</v>
+        <v>0.597</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="D72" s="32" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="E72" s="32" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="F72" s="32" t="n">
         <v>0.4</v>
       </c>
       <c r="G72" s="32" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H72" s="33" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr"/>
@@ -2523,16 +2519,16 @@
         <v>0.1</v>
       </c>
       <c r="M72" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N72" s="32" t="n">
         <v>0.4</v>
-      </c>
-      <c r="N72" s="32" t="n">
-        <v>0.5</v>
       </c>
       <c r="O72" s="32" t="n">
         <v>0.367</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>0.37</v>
+        <v>0.365</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
@@ -2641,51 +2637,51 @@
         </is>
       </c>
       <c r="B76" s="32" t="n">
-        <v>3.855</v>
+        <v>3.922</v>
       </c>
       <c r="C76" s="32" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D76" s="32" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="E76" s="32" t="n">
-        <v>3.333</v>
+        <v>3.733</v>
       </c>
       <c r="F76" s="32" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G76" s="32" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="H76" s="36" t="inlineStr">
         <is>
-          <t>22nd</t>
+          <t>15th</t>
         </is>
       </c>
       <c r="I76" s="32" t="inlineStr"/>
       <c r="J76" s="33" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="K76" s="32" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="L76" s="32" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="M76" s="32" t="n">
-        <v>4.133</v>
+        <v>4.267</v>
       </c>
       <c r="N76" s="32" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="O76" s="32" t="n">
-        <v>4.033</v>
+        <v>4.167</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>4.699</v>
+        <v>4.716</v>
       </c>
       <c r="Q76" s="35" t="inlineStr">
         <is>
@@ -2703,7 +2699,7 @@
         <v>7.735</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D77" s="32" t="inlineStr">
         <is>
@@ -2757,7 +2753,7 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>6.143</v>
+        <v>6.667</v>
       </c>
       <c r="P77" s="32" t="n">
         <v>7.854</v>
@@ -2778,7 +2774,7 @@
         <v>0.959</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>0.167</v>
+        <v>0.2</v>
       </c>
       <c r="D78" s="32" t="inlineStr">
         <is>
@@ -2857,7 +2853,7 @@
         <v>8</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>9.833</v>
+        <v>9.4</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -2911,7 +2907,7 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>7</v>
+        <v>7.333</v>
       </c>
       <c r="P79" s="32" t="n">
         <v>7.938</v>
@@ -2929,7 +2925,7 @@
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.521</v>
+        <v>0.514</v>
       </c>
       <c r="C80" s="32" t="n">
         <v>0.367</v>
@@ -2941,24 +2937,24 @@
         <v>0.267</v>
       </c>
       <c r="F80" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G80" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G80" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>12th</t>
+      <c r="H80" s="36" t="inlineStr">
+        <is>
+          <t>18th</t>
         </is>
       </c>
       <c r="I80" s="32" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J80" s="36" t="inlineStr">
-        <is>
-          <t>22nd</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J80" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="K80" s="32" t="n">
@@ -2968,16 +2964,16 @@
         <v>0.3</v>
       </c>
       <c r="M80" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N80" s="32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O80" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="N80" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O80" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
       <c r="P80" s="32" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
@@ -3116,51 +3112,51 @@
         </is>
       </c>
       <c r="B66" s="32" t="n">
-        <v>4.431</v>
+        <v>4.384</v>
       </c>
       <c r="C66" s="32" t="n">
-        <v>4.433</v>
+        <v>4.467</v>
       </c>
       <c r="D66" s="32" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="E66" s="32" t="n">
-        <v>4.067</v>
+        <v>3.533</v>
       </c>
       <c r="F66" s="32" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="G66" s="32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H66" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
+        <v>1.8</v>
+      </c>
+      <c r="H66" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
         </is>
       </c>
       <c r="I66" s="32" t="inlineStr"/>
       <c r="J66" s="33" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="K66" s="32" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="L66" s="32" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="M66" s="32" t="n">
-        <v>4.733</v>
+        <v>4.333</v>
       </c>
       <c r="N66" s="32" t="n">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="O66" s="32" t="n">
-        <v>4.3</v>
+        <v>4.267</v>
       </c>
       <c r="P66" s="32" t="n">
-        <v>3.764</v>
+        <v>3.726</v>
       </c>
       <c r="Q66" s="35" t="inlineStr">
         <is>
@@ -3178,7 +3174,7 @@
         <v>7.826</v>
       </c>
       <c r="C67" s="32" t="n">
-        <v>7.857</v>
+        <v>8</v>
       </c>
       <c r="D67" s="32" t="inlineStr">
         <is>
@@ -3232,7 +3228,7 @@
         </is>
       </c>
       <c r="O67" s="32" t="n">
-        <v>9</v>
+        <v>9.429</v>
       </c>
       <c r="P67" s="32" t="n">
         <v>7.312</v>
@@ -3253,7 +3249,7 @@
         <v>1.109</v>
       </c>
       <c r="C68" s="32" t="n">
-        <v>0.714</v>
+        <v>0.833</v>
       </c>
       <c r="D68" s="32" t="inlineStr">
         <is>
@@ -3332,7 +3328,7 @@
         <v>8.196</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>7.714</v>
+        <v>8.167</v>
       </c>
       <c r="D69" s="32" t="inlineStr">
         <is>
@@ -3386,7 +3382,7 @@
         </is>
       </c>
       <c r="O69" s="32" t="n">
-        <v>8.125</v>
+        <v>8.571</v>
       </c>
       <c r="P69" s="32" t="n">
         <v>8.561999999999999</v>
@@ -3404,51 +3400,51 @@
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>0.522</v>
+        <v>0.529</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>0.733</v>
+        <v>0.767</v>
       </c>
       <c r="D70" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F70" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E70" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>0.8</v>
-      </c>
       <c r="G70" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
+        <v>0.2</v>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
       <c r="J70" s="33" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="K70" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L70" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L70" s="32" t="n">
-        <v>0.1</v>
-      </c>
       <c r="M70" s="32" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="N70" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O70" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="O70" s="32" t="n">
-        <v>0.467</v>
-      </c>
       <c r="P70" s="32" t="n">
-        <v>0.529</v>
+        <v>0.535</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
@@ -3557,51 +3553,51 @@
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>4.792</v>
+        <v>4.795</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>3.733</v>
+        <v>3.867</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="E74" s="32" t="n">
         <v>2.867</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="H74" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
+        <v>2.6</v>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>19th</t>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="L74" s="32" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="M74" s="32" t="n">
-        <v>5.133</v>
+        <v>5.067</v>
       </c>
       <c r="N74" s="32" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>4.533</v>
+        <v>4.5</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>4.556</v>
+        <v>4.562</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
@@ -3619,7 +3615,7 @@
         <v>8.958</v>
       </c>
       <c r="C75" s="32" t="n">
-        <v>8</v>
+        <v>8.286</v>
       </c>
       <c r="D75" s="32" t="inlineStr">
         <is>
@@ -3673,7 +3669,7 @@
         </is>
       </c>
       <c r="O75" s="32" t="n">
-        <v>8.571</v>
+        <v>8.333</v>
       </c>
       <c r="P75" s="32" t="n">
         <v>8.651999999999999</v>
@@ -3694,7 +3690,7 @@
         <v>1.333</v>
       </c>
       <c r="C76" s="32" t="n">
-        <v>1.625</v>
+        <v>1.857</v>
       </c>
       <c r="D76" s="32" t="inlineStr">
         <is>
@@ -3773,7 +3769,7 @@
         <v>7.688</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>7.625</v>
+        <v>7.571</v>
       </c>
       <c r="D77" s="32" t="inlineStr">
         <is>
@@ -3827,7 +3823,7 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>9.286</v>
+        <v>8.833</v>
       </c>
       <c r="P77" s="32" t="n">
         <v>7.739</v>
@@ -3845,51 +3841,51 @@
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>0.529</v>
+        <v>0.535</v>
       </c>
       <c r="C78" s="32" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
         <v>0.4</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="36" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>0.2</v>
       </c>
       <c r="L78" s="32" t="n">
         <v>0.4</v>
       </c>
       <c r="M78" s="32" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="N78" s="32" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>0.536</v>
+        <v>0.543</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
@@ -4028,26 +4024,26 @@
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.718</v>
+        <v>4.708</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>4.4</v>
+        <v>4.467</v>
       </c>
       <c r="D70" s="32" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="E70" s="32" t="n">
-        <v>5.067</v>
+        <v>4.8</v>
       </c>
       <c r="F70" s="32" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G70" s="32" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="H70" s="33" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>8th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr">
@@ -4055,28 +4051,28 @@
           <t>★★★</t>
         </is>
       </c>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="K70" s="32" t="n">
-        <v>10.2</v>
+        <v>8.4</v>
       </c>
       <c r="L70" s="32" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M70" s="32" t="n">
-        <v>6.667</v>
+        <v>6.933</v>
       </c>
       <c r="N70" s="32" t="n">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>5.967</v>
+        <v>5.8</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>5.276</v>
+        <v>5.26</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
@@ -4094,7 +4090,7 @@
         <v>8.778</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -4148,7 +4144,7 @@
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="P71" s="32" t="n">
         <v>8.603999999999999</v>
@@ -4169,7 +4165,7 @@
         <v>0.956</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>1.167</v>
+        <v>1.4</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -4248,7 +4244,7 @@
         <v>7.244</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>7.667</v>
+        <v>8.4</v>
       </c>
       <c r="D73" s="32" t="inlineStr">
         <is>
@@ -4302,7 +4298,7 @@
         </is>
       </c>
       <c r="O73" s="32" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="P73" s="32" t="n">
         <v>8.208</v>
@@ -4320,19 +4316,19 @@
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>0.536</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>0.633</v>
+        <v>0.7</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>0.733</v>
+        <v>0.867</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G74" s="32" t="n">
         <v>1.4</v>
@@ -4347,28 +4343,28 @@
           <t>★★★</t>
         </is>
       </c>
-      <c r="J74" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
         <v>0.8</v>
       </c>
       <c r="L74" s="32" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M74" s="32" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="N74" s="32" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>1.133</v>
+        <v>1.067</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>0.822</v>
+        <v>0.838</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
@@ -4477,26 +4473,26 @@
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.211</v>
+        <v>4.156</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>5</v>
+        <v>4.967</v>
       </c>
       <c r="D78" s="32" t="n">
-        <v>5.15</v>
+        <v>4.9</v>
       </c>
       <c r="E78" s="32" t="n">
-        <v>5.133</v>
+        <v>4.867</v>
       </c>
       <c r="F78" s="32" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="G78" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H78" s="36" t="inlineStr">
-        <is>
-          <t>26th</t>
+        <v>2.2</v>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
@@ -4506,22 +4502,22 @@
         </is>
       </c>
       <c r="K78" s="32" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="L78" s="32" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="M78" s="32" t="n">
-        <v>3.267</v>
+        <v>3.067</v>
       </c>
       <c r="N78" s="32" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>4.5</v>
+        <v>4.133</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.493</v>
+        <v>4.431</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
@@ -4539,7 +4535,7 @@
         <v>7.792</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>8.6</v>
+        <v>9.25</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -4593,7 +4589,7 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>11.667</v>
+        <v>10.8</v>
       </c>
       <c r="P79" s="32" t="n">
         <v>8.467000000000001</v>
@@ -4614,7 +4610,7 @@
         <v>0.896</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -4693,7 +4689,7 @@
         <v>8.021000000000001</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>8.4</v>
+        <v>9.25</v>
       </c>
       <c r="D81" s="32" t="inlineStr">
         <is>
@@ -4747,7 +4743,7 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>6.667</v>
+        <v>7</v>
       </c>
       <c r="P81" s="32" t="n">
         <v>7.778</v>
@@ -4765,7 +4761,7 @@
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>0.466</v>
+        <v>0.459</v>
       </c>
       <c r="C82" s="32" t="n">
         <v>0.8</v>
@@ -4774,7 +4770,7 @@
         <v>0.7</v>
       </c>
       <c r="E82" s="32" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="F82" s="32" t="n">
         <v>0.6</v>
@@ -4782,9 +4778,9 @@
       <c r="G82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>14th</t>
+      <c r="H82" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="I82" s="32" t="inlineStr">
@@ -4792,7 +4788,7 @@
           <t>★</t>
         </is>
       </c>
-      <c r="J82" s="34" t="inlineStr">
+      <c r="J82" s="36" t="inlineStr">
         <is>
           <t>20th</t>
         </is>
@@ -4810,10 +4806,10 @@
         <v>0.35</v>
       </c>
       <c r="O82" s="32" t="n">
-        <v>0.7</v>
+        <v>0.533</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>0.493</v>
+        <v>0.486</v>
       </c>
       <c r="Q82" s="35" t="inlineStr">
         <is>
@@ -4952,51 +4948,55 @@
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.288</v>
+        <v>4.311</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>4.767</v>
+        <v>4.933</v>
       </c>
       <c r="D70" s="32" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="E70" s="32" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="F70" s="32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G70" s="32" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H70" s="33" t="inlineStr">
         <is>
           <t>4th</t>
         </is>
       </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>14th</t>
         </is>
       </c>
       <c r="K70" s="32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L70" s="32" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="M70" s="32" t="n">
-        <v>4.933</v>
+        <v>5.267</v>
       </c>
       <c r="N70" s="32" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>4.433</v>
+        <v>4.7</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>4.111</v>
+        <v>4.171</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>7.755</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>8.6</v>
+        <v>9.25</v>
       </c>
       <c r="P71" s="32" t="n">
         <v>7.673</v>
@@ -5089,7 +5089,7 @@
         <v>1.02</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>1.833</v>
+        <v>2</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>8.305999999999999</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>8.167</v>
+        <v>8</v>
       </c>
       <c r="D73" s="32" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="O73" s="32" t="n">
-        <v>9.6</v>
+        <v>10.75</v>
       </c>
       <c r="P73" s="32" t="n">
         <v>8.571</v>
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="C74" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>0.533</v>
+        <v>0.467</v>
       </c>
       <c r="F74" s="32" t="n">
         <v>0.5</v>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="H74" s="33" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr">
@@ -5267,9 +5267,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>16th</t>
+      <c r="J74" s="36" t="inlineStr">
+        <is>
+          <t>14th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
@@ -5279,7 +5279,7 @@
         <v>0.2</v>
       </c>
       <c r="M74" s="32" t="n">
-        <v>1.067</v>
+        <v>0.867</v>
       </c>
       <c r="N74" s="32" t="n">
         <v>0.9</v>
@@ -5288,7 +5288,7 @@
         <v>0.667</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>0.797</v>
+        <v>0.787</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
@@ -5397,26 +5397,26 @@
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.148</v>
+        <v>4.146</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>4.5</v>
+        <v>4.333</v>
       </c>
       <c r="D78" s="32" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="E78" s="32" t="n">
-        <v>4.333</v>
+        <v>4.467</v>
       </c>
       <c r="F78" s="32" t="n">
         <v>4.5</v>
       </c>
       <c r="G78" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>11th</t>
+        <v>4.8</v>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>14th</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr">
@@ -5424,28 +5424,28 @@
           <t>★</t>
         </is>
       </c>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>17th</t>
+      <c r="J78" s="36" t="inlineStr">
+        <is>
+          <t>18th</t>
         </is>
       </c>
       <c r="K78" s="32" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L78" s="32" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="M78" s="32" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O78" s="32" t="n">
         <v>3.533</v>
       </c>
-      <c r="N78" s="32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>3.7</v>
-      </c>
       <c r="P78" s="32" t="n">
-        <v>3.986</v>
+        <v>3.959</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>7.816</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>10.2</v>
+        <v>10.25</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="P79" s="32" t="n">
         <v>7.592</v>
@@ -5538,7 +5538,7 @@
         <v>1.041</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>8.592000000000001</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="D81" s="32" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>7.333</v>
+        <v>6.4</v>
       </c>
       <c r="P81" s="32" t="n">
         <v>7.776</v>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>0.622</v>
+        <v>0.613</v>
       </c>
       <c r="C82" s="32" t="n">
-        <v>0.867</v>
+        <v>0.733</v>
       </c>
       <c r="D82" s="32" t="n">
         <v>0.75</v>
@@ -5704,21 +5704,17 @@
         <v>0.6</v>
       </c>
       <c r="G82" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>11th</t>
+        <v>0.4</v>
+      </c>
+      <c r="H82" s="36" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
         </is>
       </c>
       <c r="K82" s="32" t="n">
@@ -5731,13 +5727,13 @@
         <v>0.267</v>
       </c>
       <c r="N82" s="32" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O82" s="32" t="n">
         <v>0.3</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>0.37</v>
+        <v>0.365</v>
       </c>
       <c r="Q82" s="35" t="inlineStr">
         <is>
@@ -5895,13 +5891,13 @@
       </c>
       <c r="H69" s="34" t="inlineStr">
         <is>
-          <t>20th</t>
+          <t>23rd</t>
         </is>
       </c>
       <c r="I69" s="32" t="inlineStr"/>
       <c r="J69" s="33" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="K69" s="32" t="n">
@@ -6183,11 +6179,11 @@
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
-          <t>17th</t>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
+      <c r="J73" s="36" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
@@ -6334,7 +6330,7 @@
       <c r="G77" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="H77" s="34" t="inlineStr">
+      <c r="H77" s="36" t="inlineStr">
         <is>
           <t>12th</t>
         </is>
@@ -6344,9 +6340,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="J77" s="34" t="inlineStr">
-        <is>
-          <t>20th</t>
+      <c r="J77" s="36" t="inlineStr">
+        <is>
+          <t>19th</t>
         </is>
       </c>
       <c r="K77" s="32" t="n">
@@ -6626,9 +6622,9 @@
       <c r="G81" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>28th</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
@@ -6674,7 +6670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6691,245 +6687,170 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>San Diego Padres offense vs Los Angeles Dodgers defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>4.026</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="34" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>3.933</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>7.087</v>
+        <v>4.013</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.967</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>4.5</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>6</v>
+        <v>4.167</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>6.596</v>
+        <v>3.487</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.022</v>
+        <v>7.087</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>1.2</v>
+        <v>7.25</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -6982,33 +6903,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O71" s="32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>6.596</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.348000000000001</v>
+        <v>1.022</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -7061,320 +6978,324 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O72" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>8.106</v>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8.348000000000001</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>8.106</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="C73" s="32" t="n">
+      <c r="B74" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="C74" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H73" s="36" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N73" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O73" s="32" t="n">
+      <c r="N74" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O74" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P73" s="32" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="P74" s="32" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Los Angeles Dodgers offense vs San Diego Padres defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>5.533</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>5.433</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>5.267</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J77" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>3.936</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>9.191000000000001</v>
+        <v>5.474</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.333</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>5.4</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>5.133</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>7.848</v>
+        <v>4.177</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>1.553</v>
+        <v>9.191000000000001</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -7427,33 +7348,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O79" s="32" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>7.848</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.510999999999999</v>
+        <v>1.553</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>7.2</v>
+        <v>1</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -7506,72 +7423,155 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O80" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="P80" s="32" t="n">
-        <v>8.304</v>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>8.510999999999999</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>8.304</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="32" t="n">
+      <c r="B82" s="32" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H82" s="36" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L82" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M82" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="C81" s="32" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E81" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F81" s="32" t="n">
+      <c r="N82" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O82" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P82" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L81" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M81" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N81" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O81" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="Q81" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7725,13 +7725,13 @@
       <c r="G68" s="32" t="n">
         <v>85.2</v>
       </c>
-      <c r="H68" s="34" t="inlineStr">
+      <c r="H68" s="36" t="inlineStr">
         <is>
           <t>7th</t>
         </is>
       </c>
       <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="34" t="inlineStr">
+      <c r="J68" s="36" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
@@ -7794,7 +7794,7 @@
           <t>★</t>
         </is>
       </c>
-      <c r="J69" s="34" t="inlineStr">
+      <c r="J69" s="36" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
@@ -7857,7 +7857,7 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="J70" s="36" t="inlineStr">
+      <c r="J70" s="34" t="inlineStr">
         <is>
           <t>12th</t>
         </is>
@@ -7910,7 +7910,7 @@
       <c r="G71" s="32" t="n">
         <v>0.754</v>
       </c>
-      <c r="H71" s="36" t="inlineStr">
+      <c r="H71" s="34" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
@@ -7981,7 +7981,7 @@
       <c r="G72" s="32" t="n">
         <v>32.8</v>
       </c>
-      <c r="H72" s="34" t="inlineStr">
+      <c r="H72" s="36" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
@@ -8111,7 +8111,7 @@
       <c r="G74" s="32" t="n">
         <v>11.4</v>
       </c>
-      <c r="H74" s="34" t="inlineStr">
+      <c r="H74" s="36" t="inlineStr">
         <is>
           <t>7th</t>
         </is>
@@ -8182,7 +8182,7 @@
       <c r="G75" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="H75" s="36" t="inlineStr">
+      <c r="H75" s="34" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
@@ -8347,7 +8347,7 @@
       <c r="G79" s="32" t="n">
         <v>81.8</v>
       </c>
-      <c r="H79" s="34" t="inlineStr">
+      <c r="H79" s="36" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
@@ -8406,7 +8406,7 @@
       <c r="G80" s="32" t="n">
         <v>0.525</v>
       </c>
-      <c r="H80" s="34" t="inlineStr">
+      <c r="H80" s="36" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
@@ -8416,7 +8416,7 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="J80" s="36" t="inlineStr">
+      <c r="J80" s="34" t="inlineStr">
         <is>
           <t>14th</t>
         </is>
@@ -8469,7 +8469,7 @@
       <c r="G81" s="32" t="n">
         <v>0.306</v>
       </c>
-      <c r="H81" s="34" t="inlineStr">
+      <c r="H81" s="36" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
@@ -8528,7 +8528,7 @@
       <c r="G82" s="32" t="n">
         <v>0.781</v>
       </c>
-      <c r="H82" s="34" t="inlineStr">
+      <c r="H82" s="36" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
@@ -8599,7 +8599,7 @@
       <c r="G83" s="32" t="n">
         <v>33.4</v>
       </c>
-      <c r="H83" s="34" t="inlineStr">
+      <c r="H83" s="36" t="inlineStr">
         <is>
           <t>7th</t>
         </is>
@@ -8658,7 +8658,7 @@
       <c r="G84" s="32" t="n">
         <v>18.6</v>
       </c>
-      <c r="H84" s="36" t="inlineStr">
+      <c r="H84" s="34" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
@@ -8729,7 +8729,7 @@
       <c r="G85" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="H85" s="36" t="inlineStr">
+      <c r="H85" s="34" t="inlineStr">
         <is>
           <t>14th</t>
         </is>
@@ -8800,7 +8800,7 @@
       <c r="G86" s="32" t="n">
         <v>14.8</v>
       </c>
-      <c r="H86" s="34" t="inlineStr">
+      <c r="H86" s="36" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
@@ -8938,7 +8938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9195,32 +9195,32 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>Dallas Wings @ Connecticut Sun</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 167.5</t>
+          <t>Connecticut Sun</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5700490196078432</v>
+        <v>0.29275</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-133</v>
+        <v>242</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>104</v>
+        <v>300</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 29.3% (fair +242). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9261,12 +9261,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Dallas Wings @ Connecticut Sun</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -9276,17 +9276,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Connecticut Sun</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.2907</v>
+        <v>0.3985614035087719</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>244</v>
+        <v>151</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>300</v>
+        <v>185</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 29.1% (fair +244). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9327,32 +9327,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Seattle Storm @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Over 169</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3857931034482759</v>
+        <v>0.5351415094339622</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>159</v>
+        <v>-115</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9408,17 +9408,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4026642335766423</v>
+        <v>0.3832993197278912</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 40.3% (fair +148). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9478,13 +9478,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4873893805309735</v>
+        <v>0.4853879310344827</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9540,17 +9540,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5675711538461538</v>
+        <v>0.4762660944206008</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-131</v>
+        <v>110</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-108</v>
+        <v>133</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9586,37 +9586,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx @ New York Liberty</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5889522522522523</v>
+        <v>0.5573176470588235</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-143</v>
+        <v>-126</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-122</v>
+        <v>-104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9657,32 +9657,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx @ New York Liberty</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -1.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.546819512195122</v>
+        <v>0.5675711538461538</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-121</v>
+        <v>-131</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Minnesota Lynx @ New York Liberty</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9738,17 +9738,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.404638783269962</v>
+        <v>0.5889522522522523</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>147</v>
+        <v>-143</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>163</v>
+        <v>-122</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9784,37 +9784,37 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Minnesota Lynx @ New York Liberty</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Minnesota Lynx -1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5506442307692307</v>
+        <v>0.546819512195122</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-123</v>
+        <v>-121</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9850,17 +9850,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9870,17 +9870,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.47963133640553</v>
+        <v>0.4057414448669202</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9916,17 +9916,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9936,17 +9936,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.673372027972028</v>
+        <v>0.54405</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-206</v>
+        <v>-119</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-186</v>
+        <v>-108</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 67.3% (fair -206). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9987,12 +9987,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -10002,17 +10002,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.6104065573770492</v>
+        <v>0.5498971563981042</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-157</v>
+        <v>-122</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-144</v>
+        <v>-111</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10036,7 +10036,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -157). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10045,9 +10045,471 @@
         <v/>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0.4810599078341014</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>117</v>
+      </c>
+      <c r="I20" s="13">
+        <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
+        <v/>
+      </c>
+      <c r="J20" s="16">
+        <f>IF($H$20="","",$F$20*IF($H$20&lt;0,-100/$H$20,$H$20/100)-(1-$F$20))</f>
+        <v/>
+      </c>
+      <c r="K20" s="17">
+        <f>IF($H$20="","",MAX(0,($F$20*IF($H$20&lt;0,-100/$H$20,$H$20/100)-(1-$F$20))/IF($H$20&lt;0,-100/$H$20,$H$20/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L20" s="18">
+        <f>IF($H$20="","",ROUND(MIN($K$20,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M20" s="12">
+        <f>IF($J$20="","",IF($J$20&lt;0,"Pass",IF($J$20&lt;'Settings'!$B$4,"Thin",IF($J$20&lt;0.06,"✅ Sharp band",IF($J$20&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N20" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.1% (fair +108). Your call.</t>
+        </is>
+      </c>
+      <c r="O20" s="15" t="n"/>
+      <c r="P20" s="16">
+        <f>IF(OR($H$20="",$O$20=""),"",(1+IF($H$20&lt;0,-100/$H$20,$H$20/100))/(1+IF($O$20&lt;0,-100/$O$20,$O$20/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels +1.5</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0.5626783410138249</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>-129</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I21" s="13">
+        <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
+        <v/>
+      </c>
+      <c r="J21" s="16">
+        <f>IF($H$21="","",$F$21*IF($H$21&lt;0,-100/$H$21,$H$21/100)-(1-$F$21))</f>
+        <v/>
+      </c>
+      <c r="K21" s="17">
+        <f>IF($H$21="","",MAX(0,($F$21*IF($H$21&lt;0,-100/$H$21,$H$21/100)-(1-$F$21))/IF($H$21&lt;0,-100/$H$21,$H$21/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L21" s="18">
+        <f>IF($H$21="","",ROUND(MIN($K$21,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M21" s="12">
+        <f>IF($J$21="","",IF($J$21&lt;0,"Pass",IF($J$21&lt;'Settings'!$B$4,"Thin",IF($J$21&lt;0.06,"✅ Sharp band",IF($J$21&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N21" s="19" t="inlineStr">
+        <is>
+          <t>Model 56.3% (fair -129). Your call.</t>
+        </is>
+      </c>
+      <c r="O21" s="15" t="n"/>
+      <c r="P21" s="16">
+        <f>IF(OR($H$21="",$O$21=""),"",(1+IF($H$21&lt;0,-100/$H$21,$H$21/100))/(1+IF($O$21&lt;0,-100/$O$21,$O$21/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0.6766237762237762</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>-209</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-186</v>
+      </c>
+      <c r="I22" s="13">
+        <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
+        <v/>
+      </c>
+      <c r="J22" s="16">
+        <f>IF($H$22="","",$F$22*IF($H$22&lt;0,-100/$H$22,$H$22/100)-(1-$F$22))</f>
+        <v/>
+      </c>
+      <c r="K22" s="17">
+        <f>IF($H$22="","",MAX(0,($F$22*IF($H$22&lt;0,-100/$H$22,$H$22/100)-(1-$F$22))/IF($H$22&lt;0,-100/$H$22,$H$22/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L22" s="18">
+        <f>IF($H$22="","",ROUND(MIN($K$22,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M22" s="12">
+        <f>IF($J$22="","",IF($J$22&lt;0,"Pass",IF($J$22&lt;'Settings'!$B$4,"Thin",IF($J$22&lt;0.06,"✅ Sharp band",IF($J$22&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N22" s="19" t="inlineStr">
+        <is>
+          <t>Model 67.7% (fair -209). Your call.</t>
+        </is>
+      </c>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="16">
+        <f>IF(OR($H$22="",$O$22=""),"",(1+IF($H$22&lt;0,-100/$H$22,$H$22/100))/(1+IF($O$22&lt;0,-100/$O$22,$O$22/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.4982211538461538</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>101</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="I23" s="13">
+        <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
+        <v/>
+      </c>
+      <c r="J23" s="16">
+        <f>IF($H$23="","",$F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="17">
+        <f>IF($H$23="","",MAX(0,($F$23*IF($H$23&lt;0,-100/$H$23,$H$23/100)-(1-$F$23))/IF($H$23&lt;0,-100/$H$23,$H$23/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L23" s="18">
+        <f>IF($H$23="","",ROUND(MIN($K$23,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M23" s="12">
+        <f>IF($J$23="","",IF($J$23&lt;0,"Pass",IF($J$23&lt;'Settings'!$B$4,"Thin",IF($J$23&lt;0.06,"✅ Sharp band",IF($J$23&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N23" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.8% (fair +101). Your call.</t>
+        </is>
+      </c>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="16">
+        <f>IF(OR($H$23="",$O$23=""),"",(1+IF($H$23&lt;0,-100/$H$23,$H$23/100))/(1+IF($O$23&lt;0,-100/$O$23,$O$23/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.4656306306306307</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>122</v>
+      </c>
+      <c r="I24" s="13">
+        <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
+        <v/>
+      </c>
+      <c r="J24" s="16">
+        <f>IF($H$24="","",$F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="17">
+        <f>IF($H$24="","",MAX(0,($F$24*IF($H$24&lt;0,-100/$H$24,$H$24/100)-(1-$F$24))/IF($H$24&lt;0,-100/$H$24,$H$24/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L24" s="18">
+        <f>IF($H$24="","",ROUND(MIN($K$24,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M24" s="12">
+        <f>IF($J$24="","",IF($J$24&lt;0,"Pass",IF($J$24&lt;'Settings'!$B$4,"Thin",IF($J$24&lt;0.06,"✅ Sharp band",IF($J$24&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N24" s="19" t="inlineStr">
+        <is>
+          <t>Model 46.6% (fair +115). Your call.</t>
+        </is>
+      </c>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="16">
+        <f>IF(OR($H$24="",$O$24=""),"",(1+IF($H$24&lt;0,-100/$H$24,$H$24/100))/(1+IF($O$24&lt;0,-100/$O$24,$O$24/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Seattle Storm @ Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.6166800000000001</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>-161</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-150</v>
+      </c>
+      <c r="I25" s="13">
+        <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="16">
+        <f>IF($H$25="","",$F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>IF($H$25="","",MAX(0,($F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))/IF($H$25&lt;0,-100/$H$25,$H$25/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L25" s="18">
+        <f>IF($H$25="","",ROUND(MIN($K$25,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M25" s="12">
+        <f>IF($J$25="","",IF($J$25&lt;0,"Pass",IF($J$25&lt;'Settings'!$B$4,"Thin",IF($J$25&lt;0.06,"✅ Sharp band",IF($J$25&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="19" t="inlineStr">
+        <is>
+          <t>Model 61.7% (fair -161). Your call.</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="n"/>
+      <c r="P25" s="16">
+        <f>IF(OR($H$25="",$O$25=""),"",(1+IF($H$25&lt;0,-100/$H$25,$H$25/100))/(1+IF($O$25&lt;0,-100/$O$25,$O$25/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.4805633802816902</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>113</v>
+      </c>
+      <c r="I26" s="13">
+        <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="16">
+        <f>IF($H$26="","",$F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="17">
+        <f>IF($H$26="","",MAX(0,($F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))/IF($H$26&lt;0,-100/$H$26,$H$26/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L26" s="18">
+        <f>IF($H$26="","",ROUND(MIN($K$26,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M26" s="12">
+        <f>IF($J$26="","",IF($J$26&lt;0,"Pass",IF($J$26&lt;'Settings'!$B$4,"Thin",IF($J$26&lt;0.06,"✅ Sharp band",IF($J$26&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.1% (fair +108). Your call.</t>
+        </is>
+      </c>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="16">
+        <f>IF(OR($H$26="",$O$26=""),"",(1+IF($H$26&lt;0,-100/$H$26,$H$26/100))/(1+IF($O$26&lt;0,-100/$O$26,$O$26/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J19">
+  <conditionalFormatting sqref="J5:J26">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -10069,7 +10531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10213,10 +10675,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4517511520737327</v>
+        <v>0.4548387096774194</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>117</v>
@@ -10243,7 +10705,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10279,13 +10741,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5482306306306306</v>
+        <v>0.5451552995391705</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-121</v>
+        <v>-120</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-122</v>
+        <v>-117</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10309,7 +10771,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10341,17 +10803,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.5295</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-149</v>
+        <v>-113</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10375,7 +10837,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 52.9% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10407,14 +10869,14 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4016999999999999</v>
+        <v>0.4705</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>117</v>
@@ -10441,7 +10903,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 47.1% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10549,7 +11011,7 @@
         <v>-130</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>155</v>
+        <v>-123</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -10609,13 +11071,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3266312056737589</v>
+        <v>0.3233916083916084</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -10639,7 +11101,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 32.7% (fair +206). Your call.</t>
+          <t>Model 32.3% (fair +209). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10675,10 +11137,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.673372027972028</v>
+        <v>0.6766237762237762</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-206</v>
+        <v>-209</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-186</v>
@@ -10705,7 +11167,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 67.3% (fair -206). Your call.</t>
+          <t>Model 67.7% (fair -209). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10741,10 +11203,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5336</v>
+        <v>0.5421</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-114</v>
+        <v>-118</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>116</v>
@@ -10771,7 +11233,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -114). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10807,13 +11269,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4664</v>
+        <v>0.4579</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10837,7 +11299,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +114). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10873,13 +11335,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4873893805309735</v>
+        <v>0.4853879310344827</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -10903,7 +11365,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -10939,10 +11401,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.512587665198238</v>
+        <v>0.5146017621145375</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-127</v>
@@ -10969,7 +11431,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11005,10 +11467,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5341023041474654</v>
+        <v>0.5364746543778801</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>-117</v>
@@ -11035,7 +11497,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11071,13 +11533,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4658878504672898</v>
+        <v>0.4634883720930233</v>
       </c>
       <c r="G18" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="H18" s="15" t="n">
         <v>115</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>114</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11101,7 +11563,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11137,10 +11599,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.437</v>
+        <v>0.4248</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>108</v>
@@ -11167,7 +11629,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11203,10 +11665,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5751999999999999</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-129</v>
+        <v>-135</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>109</v>
@@ -11233,7 +11695,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11250,32 +11712,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Colorado Rockies +1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5506442307692307</v>
+        <v>0.5692304347826088</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-123</v>
+        <v>-132</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-108</v>
+        <v>-130</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11299,7 +11761,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11316,32 +11778,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Miami Marlins -1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4493364928909951</v>
+        <v>0.4307929515418502</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11365,7 +11827,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11392,22 +11854,22 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5157176470588235</v>
+        <v>0.5498971563981042</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-106</v>
+        <v>-122</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-104</v>
+        <v>-111</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11431,7 +11893,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -106). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11458,22 +11920,22 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4842647058823529</v>
+        <v>0.4500961538461539</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11497,7 +11959,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +106). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11514,32 +11976,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4970098039215686</v>
+        <v>0.5252</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>101</v>
+        <v>-111</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11563,7 +12025,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 52.5% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11580,32 +12042,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5030307692307692</v>
+        <v>0.4748</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-101</v>
+        <v>111</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-108</v>
+        <v>105</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11629,7 +12091,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 47.5% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11656,22 +12118,22 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4042</v>
+        <v>0.4965196078431372</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11695,7 +12157,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +147). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11722,22 +12184,22 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5958</v>
+        <v>0.5034461538461539</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-147</v>
+        <v>-101</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>117</v>
+        <v>-108</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11761,7 +12223,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -147). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11788,22 +12250,22 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves -1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.3473</v>
+        <v>0.4072</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11827,7 +12289,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 34.7% (fair +188). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11854,22 +12316,22 @@
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.6527000000000001</v>
+        <v>0.5928</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-188</v>
+        <v>-146</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11893,7 +12355,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 65.3% (fair -188). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -11910,32 +12372,32 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Atlanta Braves -1.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5238319248826291</v>
+        <v>0.3508</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-110</v>
+        <v>185</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-113</v>
+        <v>170</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11959,7 +12421,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 35.1% (fair +185). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11976,32 +12438,32 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4761971830985915</v>
+        <v>0.6492</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>110</v>
+        <v>-185</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12025,7 +12487,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 64.9% (fair -185). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12052,22 +12514,22 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5194384615384615</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12091,7 +12553,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12118,22 +12580,22 @@
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4792999999999999</v>
+        <v>0.4805633802816902</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -12157,7 +12619,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12184,22 +12646,22 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.5907373443983402</v>
+        <v>0.5201</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-144</v>
+        <v>-108</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-141</v>
+        <v>104</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12223,7 +12685,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -144). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12250,22 +12712,22 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays -1.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.4092857142857143</v>
+        <v>0.4799</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12289,7 +12751,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +144). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12306,32 +12768,32 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.47963133640553</v>
+        <v>0.5912666666666666</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>108</v>
+        <v>-145</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>117</v>
+        <v>-140</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12355,7 +12817,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 59.1% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12372,32 +12834,32 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Tampa Bay Rays -1.5</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5204073732718895</v>
+        <v>0.4087394957983194</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-109</v>
+        <v>145</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-117</v>
+        <v>138</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12421,7 +12883,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -109). Your call.</t>
+          <t>Model 40.9% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12448,22 +12910,22 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5558</v>
+        <v>0.4810599078341014</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-125</v>
+        <v>108</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12487,7 +12949,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12514,22 +12976,22 @@
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4442</v>
+        <v>0.5189388888888889</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>125</v>
+        <v>-108</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>108</v>
+        <v>-116</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12553,7 +13015,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12580,22 +13042,22 @@
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers -1.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.356</v>
+        <v>0.5573176470588235</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>181</v>
+        <v>-126</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>178</v>
+        <v>-104</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12619,7 +13081,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12646,22 +13108,22 @@
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers +1.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.644</v>
+        <v>0.4426960784313725</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-181</v>
+        <v>126</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-130</v>
+        <v>104</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12685,7 +13147,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12702,32 +13164,32 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Texas Rangers -1.5</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.3857931034482759</v>
+        <v>0.3501</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12751,7 +13213,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 35.0% (fair +186). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12768,32 +13230,32 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Detroit Tigers +1.5</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.6142013605442177</v>
+        <v>0.6498999999999999</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-159</v>
+        <v>-186</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-194</v>
+        <v>-132</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12817,7 +13279,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 65.0% (fair -186). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12844,22 +13306,22 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4919607843137255</v>
+        <v>0.3832993197278912</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12883,7 +13345,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12910,22 +13372,22 @@
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5080196078431373</v>
+        <v>0.616708843537415</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-103</v>
+        <v>-161</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-104</v>
+        <v>-194</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12949,7 +13411,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12976,22 +13438,22 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners -1.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.3875</v>
+        <v>0.4879411764705882</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13015,7 +13477,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13042,22 +13504,22 @@
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels +1.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.6125</v>
+        <v>0.5120470588235294</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-158</v>
+        <v>-105</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>130</v>
+        <v>-104</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13081,7 +13543,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -158). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13098,32 +13560,32 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Seattle Mariners -1.5</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4026642335766423</v>
+        <v>0.4373239436619719</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>174</v>
+        <v>113</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13147,7 +13609,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 40.3% (fair +148). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13164,32 +13626,32 @@
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Los Angeles Angels +1.5</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5973428571428572</v>
+        <v>0.5626783410138249</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-148</v>
+        <v>-129</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-180</v>
+        <v>-117</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13213,7 +13675,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13240,22 +13702,22 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4454</v>
+        <v>0.3985614035087719</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13279,7 +13741,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13306,22 +13768,22 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5546</v>
+        <v>0.6014571428571428</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-125</v>
+        <v>-151</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>117</v>
+        <v>-180</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13345,7 +13807,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13372,22 +13834,22 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers -1.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.3898</v>
+        <v>0.4602</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13411,7 +13873,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +157). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13438,22 +13900,22 @@
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres +1.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.6102000000000001</v>
+        <v>0.5398000000000001</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-157</v>
+        <v>-117</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13477,7 +13939,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -157). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13489,37 +13951,37 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Los Angeles Dodgers -1.5</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.42931330472103</v>
+        <v>0.3856</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13543,7 +14005,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 38.6% (fair +159). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13555,37 +14017,37 @@
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>San Diego Padres +1.5</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5707012875536481</v>
+        <v>0.6144000000000001</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-133</v>
+        <v>-159</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-133</v>
+        <v>126</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13609,7 +14071,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 61.4% (fair -159). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13626,12 +14088,12 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -13641,17 +14103,17 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4890384615384616</v>
+        <v>0.4559447004608295</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13675,7 +14137,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13692,12 +14154,12 @@
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -13707,17 +14169,17 @@
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5109711711711712</v>
+        <v>0.54405</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-104</v>
+        <v>-119</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-122</v>
+        <v>-108</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13741,7 +14203,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13758,12 +14220,12 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -13773,17 +14235,17 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.404638783269962</v>
+        <v>0.4982211538461538</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -13807,7 +14269,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13824,12 +14286,12 @@
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -13839,17 +14301,17 @@
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5953395683453238</v>
+        <v>0.5017326923076924</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-147</v>
+        <v>-101</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>-178</v>
+        <v>-108</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -13873,7 +14335,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13890,12 +14352,12 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -13905,17 +14367,17 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.5675711538461538</v>
+        <v>0.4057414448669202</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-131</v>
+        <v>146</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>-108</v>
+        <v>163</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -13939,7 +14401,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13956,12 +14418,12 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
@@ -13971,17 +14433,17 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.432451923076923</v>
+        <v>0.5942510791366906</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>131</v>
+        <v>-146</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>108</v>
+        <v>-178</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14005,7 +14467,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +131). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14022,7 +14484,7 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
@@ -14037,17 +14499,17 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.4693087557603687</v>
+        <v>0.5675711538461538</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>113</v>
+        <v>-131</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>117</v>
+        <v>-108</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -14071,7 +14533,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14088,7 +14550,7 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
@@ -14103,17 +14565,17 @@
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.432451923076923</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-113</v>
+        <v>131</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>-122</v>
+        <v>108</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -14137,7 +14599,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 43.2% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14154,12 +14616,12 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -14169,17 +14631,17 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.5629</v>
+        <v>0.4656306306306307</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>-129</v>
+        <v>115</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -14203,7 +14665,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14220,12 +14682,12 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -14235,14 +14697,14 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.4371</v>
+        <v>0.5343819819819819</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>129</v>
+        <v>-115</v>
       </c>
       <c r="H66" s="15" t="n">
         <v>-122</v>
@@ -14269,7 +14731,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14286,12 +14748,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -14301,17 +14763,17 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5033</v>
+        <v>0.4762660944206008</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-101</v>
+        <v>110</v>
       </c>
       <c r="H67" s="15" t="n">
-        <v>-117</v>
+        <v>133</v>
       </c>
       <c r="I67" s="13">
         <f>IF($H$67="","",IF($H$67&lt;0,-$H$67/(-$H$67+100),100/($H$67+100)))</f>
@@ -14335,7 +14797,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14352,12 +14814,12 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -14367,17 +14829,17 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4967</v>
+        <v>0.5237231759656652</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>101</v>
+        <v>-110</v>
       </c>
       <c r="H68" s="15" t="n">
-        <v>138</v>
+        <v>-133</v>
       </c>
       <c r="I68" s="13">
         <f>IF($H$68="","",IF($H$68&lt;0,-$H$68/(-$H$68+100),100/($H$68+100)))</f>
@@ -14401,7 +14863,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14418,12 +14880,12 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -14433,17 +14895,17 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.5057826923076922</v>
+        <v>0.5046</v>
       </c>
       <c r="G69" s="14" t="n">
         <v>-102</v>
       </c>
       <c r="H69" s="15" t="n">
-        <v>-108</v>
+        <v>-117</v>
       </c>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
@@ -14467,7 +14929,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14484,12 +14946,12 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -14499,17 +14961,17 @@
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4942039215686274</v>
+        <v>0.4955</v>
       </c>
       <c r="G70" s="14" t="n">
         <v>102</v>
       </c>
       <c r="H70" s="15" t="n">
-        <v>-104</v>
+        <v>138</v>
       </c>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
@@ -14533,7 +14995,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14550,12 +15012,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -14565,17 +15027,17 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4907</v>
+        <v>0.5059903846153846</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>104</v>
+        <v>-102</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>117</v>
+        <v>-108</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -14599,7 +15061,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14616,12 +15078,12 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -14631,17 +15093,17 @@
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5093</v>
+        <v>0.4939999999999999</v>
       </c>
       <c r="G72" s="14" t="n">
+        <v>102</v>
+      </c>
+      <c r="H72" s="15" t="n">
         <v>-104</v>
-      </c>
-      <c r="H72" s="15" t="n">
-        <v>108</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -14665,7 +15127,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14682,12 +15144,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -14697,17 +15159,17 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4658215962441314</v>
+        <v>0.4948</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14731,7 +15193,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14748,12 +15210,12 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -14763,17 +15225,17 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5341832599118943</v>
+        <v>0.5052</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-115</v>
+        <v>-102</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-127</v>
+        <v>108</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -14797,7 +15259,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14814,12 +15276,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -14829,16 +15291,18 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.6102</v>
+        <v>0.471924882629108</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-157</v>
-      </c>
-      <c r="H75" s="15" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="H75" s="15" t="n">
+        <v>113</v>
+      </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
         <v/>
@@ -14861,7 +15325,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -157). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14878,12 +15342,12 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -14893,16 +15357,18 @@
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.3898</v>
+        <v>0.5280760563380281</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>157</v>
-      </c>
-      <c r="H76" s="15" t="n"/>
+        <v>-112</v>
+      </c>
+      <c r="H76" s="15" t="n">
+        <v>-113</v>
+      </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
         <v/>
@@ -14925,7 +15391,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +157). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14942,12 +15408,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -14957,14 +15423,14 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4019</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>149</v>
+        <v>-157</v>
       </c>
       <c r="H77" s="15" t="n"/>
       <c r="I77" s="13">
@@ -14989,7 +15455,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 61.0% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15006,12 +15472,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -15021,14 +15487,14 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5981</v>
+        <v>0.3896</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-149</v>
+        <v>157</v>
       </c>
       <c r="H78" s="15" t="n"/>
       <c r="I78" s="13">
@@ -15053,7 +15519,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 39.0% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15070,7 +15536,7 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -15085,14 +15551,14 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5278</v>
+        <v>0.4045</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-112</v>
+        <v>147</v>
       </c>
       <c r="H79" s="15" t="n"/>
       <c r="I79" s="13">
@@ -15117,7 +15583,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15134,7 +15600,7 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
@@ -15149,14 +15615,14 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4722</v>
+        <v>0.5955</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>112</v>
+        <v>-147</v>
       </c>
       <c r="H80" s="15" t="n"/>
       <c r="I80" s="13">
@@ -15181,7 +15647,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 59.6% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15190,9 +15656,137 @@
         <v/>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>0.5266</v>
+      </c>
+      <c r="G81" s="14" t="n">
+        <v>-111</v>
+      </c>
+      <c r="H81" s="15" t="n"/>
+      <c r="I81" s="13">
+        <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
+        <v/>
+      </c>
+      <c r="J81" s="16">
+        <f>IF($H$81="","",$F$81*IF($H$81&lt;0,-100/$H$81,$H$81/100)-(1-$F$81))</f>
+        <v/>
+      </c>
+      <c r="K81" s="17">
+        <f>IF($H$81="","",MAX(0,($F$81*IF($H$81&lt;0,-100/$H$81,$H$81/100)-(1-$F$81))/IF($H$81&lt;0,-100/$H$81,$H$81/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L81" s="18">
+        <f>IF($H$81="","",ROUND(MIN($K$81,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M81" s="12">
+        <f>IF($J$81="","",IF($J$81&lt;0,"Pass",IF($J$81&lt;'Settings'!$B$4,"Thin",IF($J$81&lt;0.06,"✅ Sharp band",IF($J$81&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N81" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.7% (fair -111). Your call.</t>
+        </is>
+      </c>
+      <c r="O81" s="15" t="n"/>
+      <c r="P81" s="16">
+        <f>IF(OR($H$81="",$O$81=""),"",(1+IF($H$81&lt;0,-100/$H$81,$H$81/100))/(1+IF($O$81&lt;0,-100/$O$81,$O$81/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E82" s="20" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="n">
+        <v>0.4734</v>
+      </c>
+      <c r="G82" s="14" t="n">
+        <v>111</v>
+      </c>
+      <c r="H82" s="15" t="n"/>
+      <c r="I82" s="13">
+        <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
+        <v/>
+      </c>
+      <c r="J82" s="16">
+        <f>IF($H$82="","",$F$82*IF($H$82&lt;0,-100/$H$82,$H$82/100)-(1-$F$82))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF($H$82="","",MAX(0,($F$82*IF($H$82&lt;0,-100/$H$82,$H$82/100)-(1-$F$82))/IF($H$82&lt;0,-100/$H$82,$H$82/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L82" s="18">
+        <f>IF($H$82="","",ROUND(MIN($K$82,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M82" s="12">
+        <f>IF($J$82="","",IF($J$82&lt;0,"Pass",IF($J$82&lt;'Settings'!$B$4,"Thin",IF($J$82&lt;0.06,"✅ Sharp band",IF($J$82&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N82" s="19" t="inlineStr">
+        <is>
+          <t>Model 47.3% (fair +111). Your call.</t>
+        </is>
+      </c>
+      <c r="O82" s="15" t="n"/>
+      <c r="P82" s="16">
+        <f>IF(OR($H$82="",$O$82=""),"",(1+IF($H$82&lt;0,-100/$H$82,$H$82/100))/(1+IF($O$82&lt;0,-100/$O$82,$O$82/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J80">
+  <conditionalFormatting sqref="J5:J82">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -15628,7 +16222,7 @@
         <v>-153</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -15754,13 +16348,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.7093350119904077</v>
+        <v>0.7072282051282052</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-244</v>
+        <v>-242</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-317</v>
+        <v>-290</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -15784,7 +16378,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 70.9% (fair -244). Your call.</t>
+          <t>Model 70.7% (fair -242). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -15820,10 +16414,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.2907</v>
+        <v>0.29275</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>300</v>
@@ -15850,7 +16444,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 29.1% (fair +244). Your call.</t>
+          <t>Model 29.3% (fair +242). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -15886,13 +16480,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4191079812206573</v>
+        <v>0.4191176470588235</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>139</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -15958,7 +16552,7 @@
         <v>-139</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -16024,7 +16618,7 @@
         <v>-114</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -16090,7 +16684,7 @@
         <v>114</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -16150,13 +16744,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.3895951417004049</v>
+        <v>0.3833203125</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -16180,7 +16774,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +157). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -16216,13 +16810,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6104065573770492</v>
+        <v>0.6166800000000001</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-157</v>
+        <v>-161</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-144</v>
+        <v>-150</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -16246,7 +16840,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -157). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -16278,17 +16872,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 167.5</t>
+          <t>Over 169</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5700490196078432</v>
+        <v>0.5351415094339622</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-133</v>
+        <v>-115</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -16312,7 +16906,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -16344,17 +16938,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 167.5</t>
+          <t>Under 169</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.43</v>
+        <v>0.4648</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -16378,7 +16972,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +133). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -16420,7 +17014,7 @@
         <v>105</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -16486,7 +17080,7 @@
         <v>-105</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -17074,13 +17668,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5206326923076923</v>
+        <v>0.5206666666666666</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>-109</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -17146,7 +17740,7 @@
         <v>109</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -17206,10 +17800,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.50375</v>
+        <v>0.5085</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>100</v>
@@ -17236,7 +17830,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -17272,13 +17866,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4962288461538461</v>
+        <v>0.4915</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -17302,7 +17896,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 49.1% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -17989,26 +18583,26 @@
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>5.038</v>
+        <v>5.051</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>5.533</v>
+        <v>5.667</v>
       </c>
       <c r="D70" s="32" t="n">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="E70" s="32" t="n">
-        <v>5.533</v>
+        <v>5.8</v>
       </c>
       <c r="F70" s="32" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="G70" s="32" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H70" s="33" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr">
@@ -18018,26 +18612,26 @@
       </c>
       <c r="J70" s="34" t="inlineStr">
         <is>
-          <t>18th</t>
+          <t>21st</t>
         </is>
       </c>
       <c r="K70" s="32" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="L70" s="32" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="M70" s="32" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="N70" s="32" t="n">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>4.567</v>
+        <v>4.633</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>4.763</v>
+        <v>4.779</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
@@ -18055,7 +18649,7 @@
         <v>8.811999999999999</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -18109,7 +18703,7 @@
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>8.75</v>
+        <v>9.667</v>
       </c>
       <c r="P71" s="32" t="n">
         <v>9.319000000000001</v>
@@ -18130,7 +18724,7 @@
         <v>1.188</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -18209,7 +18803,7 @@
         <v>9.708</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="D73" s="32" t="inlineStr">
         <is>
@@ -18263,7 +18857,7 @@
         </is>
       </c>
       <c r="O73" s="32" t="n">
-        <v>8.25</v>
+        <v>9.333</v>
       </c>
       <c r="P73" s="32" t="n">
         <v>9.276999999999999</v>
@@ -18281,26 +18875,26 @@
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="C74" s="32" t="n">
         <v>0.5</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="E74" s="32" t="n">
         <v>0.4</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H74" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
+        <v>0</v>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
@@ -18322,10 +18916,10 @@
         <v>0.6</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.533</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>0.534</v>
+        <v>0.527</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
@@ -18434,26 +19028,26 @@
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.553</v>
+        <v>4.623</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>5.333</v>
+        <v>5.6</v>
       </c>
       <c r="D78" s="32" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="E78" s="32" t="n">
-        <v>6.533</v>
+        <v>6.733</v>
       </c>
       <c r="F78" s="32" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="G78" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>13th</t>
+        <v>6.4</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr">
@@ -18461,28 +19055,28 @@
           <t>★★★</t>
         </is>
       </c>
-      <c r="J78" s="36" t="inlineStr">
+      <c r="J78" s="34" t="inlineStr">
         <is>
           <t>28th</t>
         </is>
       </c>
       <c r="K78" s="32" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="L78" s="32" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="M78" s="32" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="N78" s="32" t="n">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>5.667</v>
+        <v>5.767</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.744</v>
+        <v>4.81</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
@@ -18500,7 +19094,7 @@
         <v>7.234</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>5.75</v>
+        <v>6.667</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -18554,7 +19148,7 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="P79" s="32" t="n">
         <v>7.792</v>
@@ -18575,7 +19169,7 @@
         <v>1.213</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>1.25</v>
+        <v>1.333</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -18654,7 +19248,7 @@
         <v>8.426</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>9.75</v>
+        <v>9.333</v>
       </c>
       <c r="D81" s="32" t="inlineStr">
         <is>
@@ -18708,7 +19302,7 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>11.8</v>
+        <v>11.25</v>
       </c>
       <c r="P81" s="32" t="n">
         <v>9.292</v>
@@ -18726,43 +19320,43 @@
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>0.589</v>
+        <v>0.581</v>
       </c>
       <c r="C82" s="32" t="n">
         <v>0.5</v>
       </c>
       <c r="D82" s="32" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="E82" s="32" t="n">
         <v>0.8</v>
       </c>
       <c r="F82" s="32" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H82" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
+        <v>0.4</v>
+      </c>
+      <c r="H82" s="36" t="inlineStr">
+        <is>
+          <t>13th</t>
         </is>
       </c>
       <c r="I82" s="32" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J82" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>24th</t>
         </is>
       </c>
       <c r="K82" s="32" t="n">
         <v>0.6</v>
       </c>
       <c r="L82" s="32" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M82" s="32" t="n">
         <v>0.6</v>
@@ -18774,7 +19368,7 @@
         <v>0.467</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>0.411</v>
+        <v>0.405</v>
       </c>
       <c r="Q82" s="35" t="inlineStr">
         <is>
@@ -18913,7 +19507,7 @@
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>4.028</v>
+        <v>4</v>
       </c>
       <c r="C69" s="32" t="n">
         <v>3.733</v>
@@ -18922,21 +19516,21 @@
         <v>4</v>
       </c>
       <c r="E69" s="32" t="n">
-        <v>4.333</v>
+        <v>4.267</v>
       </c>
       <c r="F69" s="32" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="G69" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>14th</t>
+        <v>4</v>
+      </c>
+      <c r="H69" s="36" t="inlineStr">
+        <is>
+          <t>17th</t>
         </is>
       </c>
       <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="34" t="inlineStr">
+      <c r="J69" s="36" t="inlineStr">
         <is>
           <t>12th</t>
         </is>
@@ -18945,19 +19539,19 @@
         <v>3.8</v>
       </c>
       <c r="L69" s="32" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="M69" s="32" t="n">
-        <v>3</v>
+        <v>3.133</v>
       </c>
       <c r="N69" s="32" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="O69" s="32" t="n">
-        <v>4.067</v>
+        <v>4</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>3.795</v>
+        <v>3.77</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
@@ -18975,7 +19569,7 @@
         <v>7.404</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>7.167</v>
+        <v>7</v>
       </c>
       <c r="D70" s="32" t="inlineStr">
         <is>
@@ -19029,7 +19623,7 @@
         </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="P70" s="32" t="n">
         <v>7.174</v>
@@ -19050,7 +19644,7 @@
         <v>1.213</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>1.333</v>
+        <v>1.6</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -19129,7 +19723,7 @@
         <v>9.532</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -19183,7 +19777,7 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>10.4</v>
+        <v>10.75</v>
       </c>
       <c r="P72" s="32" t="n">
         <v>9.630000000000001</v>
@@ -19201,7 +19795,7 @@
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="C73" s="32" t="n">
         <v>0.533</v>
@@ -19210,7 +19804,7 @@
         <v>0.55</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>0.733</v>
+        <v>0.667</v>
       </c>
       <c r="F73" s="32" t="n">
         <v>0.3</v>
@@ -19220,7 +19814,7 @@
       </c>
       <c r="H73" s="33" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr">
@@ -19228,7 +19822,7 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="J73" s="34" t="inlineStr">
+      <c r="J73" s="36" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
@@ -19243,13 +19837,13 @@
         <v>0.2</v>
       </c>
       <c r="N73" s="32" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O73" s="32" t="n">
         <v>0.367</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>0.408</v>
+        <v>0.403</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
@@ -19358,26 +19952,26 @@
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>5.096</v>
+        <v>5.081</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>5.7</v>
+        <v>5.667</v>
       </c>
       <c r="D77" s="32" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="E77" s="32" t="n">
         <v>4.267</v>
       </c>
       <c r="F77" s="32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G77" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H77" s="34" t="inlineStr">
-        <is>
-          <t>15th</t>
+        <v>4.2</v>
+      </c>
+      <c r="H77" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr">
@@ -19385,7 +19979,7 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="J77" s="36" t="inlineStr">
+      <c r="J77" s="34" t="inlineStr">
         <is>
           <t>26th</t>
         </is>
@@ -19394,19 +19988,19 @@
         <v>6.4</v>
       </c>
       <c r="L77" s="32" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="M77" s="32" t="n">
-        <v>4.467</v>
+        <v>4.4</v>
       </c>
       <c r="N77" s="32" t="n">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="O77" s="32" t="n">
         <v>4.867</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
@@ -19424,7 +20018,7 @@
         <v>7.935</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="D78" s="32" t="inlineStr">
         <is>
@@ -19478,7 +20072,7 @@
         </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>8.667</v>
+        <v>9</v>
       </c>
       <c r="P78" s="32" t="n">
         <v>8.106</v>
@@ -19499,7 +20093,7 @@
         <v>0.739</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -19578,7 +20172,7 @@
         <v>8.151999999999999</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -19632,7 +20226,7 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="P80" s="32" t="n">
         <v>7.404</v>
@@ -19650,51 +20244,51 @@
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>0.577</v>
+        <v>0.597</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>0.533</v>
+        <v>0.6</v>
       </c>
       <c r="D81" s="32" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E81" s="32" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="F81" s="32" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G81" s="32" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="H81" s="36" t="inlineStr">
         <is>
-          <t>25th</t>
+          <t>12th</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
       <c r="J81" s="33" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>9th</t>
         </is>
       </c>
       <c r="K81" s="32" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L81" s="32" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M81" s="32" t="n">
-        <v>0.133</v>
+        <v>0.267</v>
       </c>
       <c r="N81" s="32" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="O81" s="32" t="n">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>0.507</v>
+        <v>0.528</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>

--- a/data/output/workbook/2026-07-02.xlsx
+++ b/data/output/workbook/2026-07-02.xlsx
@@ -431,7 +431,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10096500"/>
+    <ext cx="10125075" cy="10506075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -491,7 +491,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10029825"/>
+    <ext cx="10125075" cy="10429875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10696575"/>
+    <ext cx="10125075" cy="10277475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02 06:01</t>
+          <t>2026-07-02 08:14</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,887 +1175,887 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="29" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>Miami Marlins offense vs Colorado Rockies defense</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="30" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B65" s="30" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C65" s="30" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D65" s="30" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E65" s="30" t="inlineStr">
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F65" s="30" t="inlineStr">
+      <c r="F68" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G65" s="30" t="inlineStr">
+      <c r="G68" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H65" s="30" t="inlineStr">
+      <c r="H68" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I65" s="30" t="inlineStr">
+      <c r="I68" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J65" s="30" t="inlineStr">
+      <c r="J68" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K65" s="30" t="inlineStr">
+      <c r="K68" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L65" s="30" t="inlineStr">
+      <c r="L68" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M65" s="30" t="inlineStr">
+      <c r="M68" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N65" s="30" t="inlineStr">
+      <c r="N68" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O65" s="30" t="inlineStr">
+      <c r="O68" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P65" s="30" t="inlineStr">
+      <c r="P68" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q65" s="30" t="inlineStr">
+      <c r="Q68" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="n">
-        <v>4.526</v>
-      </c>
-      <c r="C66" s="32" t="n">
-        <v>4.833</v>
-      </c>
-      <c r="D66" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E66" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="F66" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G66" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="H66" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J66" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="L66" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M66" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N66" s="32" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>6.567</v>
-      </c>
-      <c r="P66" s="32" t="n">
-        <v>5.697</v>
-      </c>
-      <c r="Q66" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>8.286</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="D67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H67" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>7.816</v>
+        <v>4.526</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.833</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>5.85</v>
       </c>
       <c r="O69" s="32" t="n">
-        <v>6.8</v>
+        <v>6.567</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>7.28</v>
+        <v>5.697</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>8.286</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>7.816</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B70" s="32" t="n">
+      <c r="B73" s="32" t="n">
         <v>0.527</v>
       </c>
-      <c r="C70" s="32" t="n">
+      <c r="C73" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="D70" s="32" t="n">
+      <c r="D73" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E70" s="32" t="n">
+      <c r="E73" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F70" s="32" t="n">
+      <c r="F73" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="G70" s="32" t="n">
+      <c r="G73" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H70" s="36" t="inlineStr">
+      <c r="H73" s="36" t="inlineStr">
         <is>
           <t>15th</t>
         </is>
       </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="36" t="inlineStr">
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="36" t="inlineStr">
         <is>
           <t>15th</t>
         </is>
       </c>
-      <c r="K70" s="32" t="n">
+      <c r="K73" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L70" s="32" t="n">
+      <c r="L73" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="M70" s="32" t="n">
+      <c r="M73" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="N70" s="32" t="n">
+      <c r="N73" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="O70" s="32" t="n">
+      <c r="O73" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="P70" s="32" t="n">
+      <c r="P73" s="32" t="n">
         <v>0.68</v>
       </c>
-      <c r="Q70" s="35" t="inlineStr">
+      <c r="Q73" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="29" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>Colorado Rockies offense vs Miami Marlins defense</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="30" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B73" s="30" t="inlineStr">
+      <c r="B76" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C73" s="30" t="inlineStr">
+      <c r="C76" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D73" s="30" t="inlineStr">
+      <c r="D76" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E73" s="30" t="inlineStr">
+      <c r="E76" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F73" s="30" t="inlineStr">
+      <c r="F76" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G73" s="30" t="inlineStr">
+      <c r="G76" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H73" s="30" t="inlineStr">
+      <c r="H76" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I73" s="30" t="inlineStr">
+      <c r="I76" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J73" s="30" t="inlineStr">
+      <c r="J76" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K73" s="30" t="inlineStr">
+      <c r="K76" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L73" s="30" t="inlineStr">
+      <c r="L76" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M73" s="30" t="inlineStr">
+      <c r="M76" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N73" s="30" t="inlineStr">
+      <c r="N76" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O73" s="30" t="inlineStr">
+      <c r="O76" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P73" s="30" t="inlineStr">
+      <c r="P76" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q73" s="30" t="inlineStr">
+      <c r="Q76" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>4.658</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>4.184</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="D75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>7.694</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>8.92</v>
+        <v>4.658</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.8</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>3.15</v>
       </c>
       <c r="O77" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>8.531000000000001</v>
+        <v>4.184</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>7.694</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q79" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>8.531000000000001</v>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B78" s="32" t="n">
+      <c r="B81" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="C78" s="32" t="n">
+      <c r="C81" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="D78" s="32" t="n">
+      <c r="D81" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E78" s="32" t="n">
+      <c r="E81" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="F78" s="32" t="n">
+      <c r="F81" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G78" s="32" t="n">
+      <c r="G81" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H78" s="33" t="inlineStr">
+      <c r="H81" s="33" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="33" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="K78" s="32" t="n">
+      <c r="K81" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L78" s="32" t="n">
+      <c r="L81" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M78" s="32" t="n">
+      <c r="M81" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="N78" s="32" t="n">
+      <c r="N81" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O78" s="32" t="n">
+      <c r="O81" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="P78" s="32" t="n">
+      <c r="P81" s="32" t="n">
         <v>0.635</v>
       </c>
-      <c r="Q78" s="35" t="inlineStr">
+      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -2994,7 +2994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3011,324 +3011,170 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="29" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
         <is>
           <t>St. Louis Cardinals offense vs Atlanta Braves defense</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="30" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B65" s="30" t="inlineStr">
+      <c r="B67" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C65" s="30" t="inlineStr">
+      <c r="C67" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D65" s="30" t="inlineStr">
+      <c r="D67" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E65" s="30" t="inlineStr">
+      <c r="E67" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F65" s="30" t="inlineStr">
+      <c r="F67" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G65" s="30" t="inlineStr">
+      <c r="G67" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H65" s="30" t="inlineStr">
+      <c r="H67" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I65" s="30" t="inlineStr">
+      <c r="I67" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J65" s="30" t="inlineStr">
+      <c r="J67" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K65" s="30" t="inlineStr">
+      <c r="K67" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L65" s="30" t="inlineStr">
+      <c r="L67" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M65" s="30" t="inlineStr">
+      <c r="M67" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N65" s="30" t="inlineStr">
+      <c r="N67" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O65" s="30" t="inlineStr">
+      <c r="O67" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P65" s="30" t="inlineStr">
+      <c r="P67" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q65" s="30" t="inlineStr">
+      <c r="Q67" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="n">
-        <v>4.384</v>
-      </c>
-      <c r="C66" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="D66" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E66" s="32" t="n">
-        <v>3.533</v>
-      </c>
-      <c r="F66" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G66" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H66" s="34" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr"/>
-      <c r="J66" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L66" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="M66" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="N66" s="32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="P66" s="32" t="n">
-        <v>3.726</v>
-      </c>
-      <c r="Q66" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>7.826</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="D67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H67" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>9.429</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>7.312</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B68" s="32" t="n">
-        <v>1.109</v>
+        <v>4.384</v>
       </c>
       <c r="C68" s="32" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.467</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H68" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
         </is>
       </c>
       <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J68" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>3.726</v>
       </c>
       <c r="Q68" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>8.196</v>
+        <v>7.826</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>8.167</v>
+        <v>8</v>
       </c>
       <c r="D69" s="32" t="inlineStr">
         <is>
@@ -3382,394 +3228,394 @@
         </is>
       </c>
       <c r="O69" s="32" t="n">
-        <v>8.571</v>
+        <v>9.429</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>8.561999999999999</v>
+        <v>7.312</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>8.196</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>8.167</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>8.571</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>8.561999999999999</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B70" s="32" t="n">
+      <c r="B72" s="32" t="n">
         <v>0.529</v>
       </c>
-      <c r="C70" s="32" t="n">
+      <c r="C72" s="32" t="n">
         <v>0.767</v>
       </c>
-      <c r="D70" s="32" t="n">
+      <c r="D72" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="E70" s="32" t="n">
+      <c r="E72" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="F70" s="32" t="n">
+      <c r="F72" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="G70" s="32" t="n">
+      <c r="G72" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H70" s="34" t="inlineStr">
+      <c r="H72" s="34" t="inlineStr">
         <is>
           <t>26th</t>
         </is>
       </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="33" t="inlineStr">
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="33" t="inlineStr">
         <is>
           <t>6th</t>
         </is>
       </c>
-      <c r="K70" s="32" t="n">
+      <c r="K72" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L70" s="32" t="n">
+      <c r="L72" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M70" s="32" t="n">
+      <c r="M72" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="N70" s="32" t="n">
+      <c r="N72" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="O70" s="32" t="n">
+      <c r="O72" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="P70" s="32" t="n">
+      <c r="P72" s="32" t="n">
         <v>0.535</v>
       </c>
-      <c r="Q70" s="35" t="inlineStr">
+      <c r="Q72" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="29" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
         <is>
           <t>Atlanta Braves offense vs St. Louis Cardinals defense</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="30" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B73" s="30" t="inlineStr">
+      <c r="B75" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C73" s="30" t="inlineStr">
+      <c r="C75" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D73" s="30" t="inlineStr">
+      <c r="D75" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E73" s="30" t="inlineStr">
+      <c r="E75" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F73" s="30" t="inlineStr">
+      <c r="F75" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G73" s="30" t="inlineStr">
+      <c r="G75" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H73" s="30" t="inlineStr">
+      <c r="H75" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I73" s="30" t="inlineStr">
+      <c r="I75" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J73" s="30" t="inlineStr">
+      <c r="J75" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K73" s="30" t="inlineStr">
+      <c r="K75" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L73" s="30" t="inlineStr">
+      <c r="L75" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M73" s="30" t="inlineStr">
+      <c r="M75" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N73" s="30" t="inlineStr">
+      <c r="N75" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O73" s="30" t="inlineStr">
+      <c r="O75" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P73" s="30" t="inlineStr">
+      <c r="P75" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q73" s="30" t="inlineStr">
+      <c r="Q75" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>4.795</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>2.867</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>4.562</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>8.958</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>8.286</v>
-      </c>
-      <c r="D75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>8.651999999999999</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B76" s="32" t="n">
-        <v>1.333</v>
+        <v>4.795</v>
       </c>
       <c r="C76" s="32" t="n">
-        <v>1.857</v>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.867</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>2.867</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J76" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>4.562</v>
       </c>
       <c r="Q76" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>7.688</v>
+        <v>8.958</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>7.571</v>
+        <v>8.286</v>
       </c>
       <c r="D77" s="32" t="inlineStr">
         <is>
@@ -3823,71 +3669,225 @@
         </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>8.833</v>
+        <v>8.333</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>7.739</v>
+        <v>8.651999999999999</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>7.688</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>7.571</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>8.833</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>7.739</v>
+      </c>
+      <c r="Q79" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B78" s="32" t="n">
+      <c r="B80" s="32" t="n">
         <v>0.535</v>
       </c>
-      <c r="C78" s="32" t="n">
+      <c r="C80" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="D78" s="32" t="n">
+      <c r="D80" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="E78" s="32" t="n">
+      <c r="E80" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="F78" s="32" t="n">
+      <c r="F80" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="G78" s="32" t="n">
+      <c r="G80" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H78" s="36" t="inlineStr">
+      <c r="H80" s="36" t="inlineStr">
         <is>
           <t>20th</t>
         </is>
       </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="36" t="inlineStr">
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="36" t="inlineStr">
         <is>
           <t>16th</t>
         </is>
       </c>
-      <c r="K78" s="32" t="n">
+      <c r="K80" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L78" s="32" t="n">
+      <c r="L80" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M78" s="32" t="n">
+      <c r="M80" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N78" s="32" t="n">
+      <c r="N80" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="O78" s="32" t="n">
+      <c r="O80" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="P78" s="32" t="n">
+      <c r="P80" s="32" t="n">
         <v>0.543</v>
       </c>
-      <c r="Q78" s="35" t="inlineStr">
+      <c r="Q80" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6670,7 +6670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6687,891 +6687,891 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
+        <is>
+          <t>San Diego Padres offense vs Los Angeles Dodgers defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B66" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C66" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D66" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E66" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F66" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G66" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H66" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I66" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J66" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K66" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L66" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M66" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N66" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O66" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P66" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q66" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>4.013</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>3.967</v>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E67" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F67" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G67" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H67" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="36" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L67" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M67" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="N67" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O67" s="32" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="P67" s="32" t="n">
+        <v>3.487</v>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>San Diego Padres offense vs Los Angeles Dodgers defense</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>7.087</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>6.596</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.013</v>
+        <v>8.348000000000001</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>3.967</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
+        <v>8.5</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>4.5</v>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>4.167</v>
+        <v>7.75</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>3.487</v>
+        <v>8.106</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers offense vs San Diego Padres defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B74" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C74" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D74" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E74" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F74" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G74" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H74" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I74" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J74" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K74" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L74" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M74" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N74" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O74" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P74" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q74" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>5.474</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H75" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J75" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L75" s="32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M75" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N75" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O75" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>4.177</v>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
           <t>Hits/G</t>
         </is>
       </c>
-      <c r="B71" s="32" t="n">
-        <v>7.087</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>6.596</v>
-      </c>
-      <c r="Q71" s="35" t="inlineStr">
+      <c r="B76" s="32" t="n">
+        <v>9.191000000000001</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>7.848</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
         <is>
           <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
         <is>
           <t>HR/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
-        <v>1.022</v>
-      </c>
-      <c r="C72" s="32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q72" s="35" t="inlineStr">
+      <c r="B77" s="32" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
         <is>
           <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>8.348000000000001</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>8.106</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers offense vs San Diego Padres defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>5.474</v>
+        <v>8.510999999999999</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>5.4</v>
+        <v>7.75</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>5.133</v>
+        <v>5.5</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.177</v>
+        <v>8.304</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>9.191000000000001</v>
+        <v>0.658</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.733</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H79" s="36" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>0.75</v>
       </c>
       <c r="O79" s="32" t="n">
-        <v>8.75</v>
+        <v>0.6</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.848</v>
+        <v>0.5</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B80" s="32" t="n">
-        <v>1.553</v>
-      </c>
-      <c r="C80" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q80" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>8.510999999999999</v>
-      </c>
-      <c r="C81" s="32" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>8.304</v>
-      </c>
-      <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.658</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H82" s="36" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8938,7 +8938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9082,13 +9082,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6154460093896714</v>
+        <v>0.6154326923076923</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-160</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9148,13 +9148,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3411484593837535</v>
+        <v>0.3383243243243243</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 34.1% (fair +193). Your call.</t>
+          <t>Model 33.8% (fair +196). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.29275</v>
+        <v>0.293875</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>300</v>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 29.3% (fair +242). Your call.</t>
+          <t>Model 29.4% (fair +240). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9261,12 +9261,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -9276,17 +9276,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3985614035087719</v>
+        <v>0.3836734693877552</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 38.4% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9327,32 +9327,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Over 169</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5351415094339622</v>
+        <v>0.403525179856115</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-115</v>
+        <v>148</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 40.4% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9388,17 +9388,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9408,17 +9408,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.3832993197278912</v>
+        <v>0.4759656652360515</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>194</v>
+        <v>133</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9459,32 +9459,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Seattle Storm @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Over 168</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4853879310344827</v>
+        <v>0.5584752475247525</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>106</v>
+        <v>-126</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>132</v>
+        <v>-102</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9540,17 +9540,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4762660944206008</v>
+        <v>0.5675711538461538</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>110</v>
+        <v>-131</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>133</v>
+        <v>-108</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9591,12 +9591,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9606,17 +9606,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 6.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5573176470588235</v>
+        <v>0.5667923076923076</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-126</v>
+        <v>-131</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9657,12 +9657,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Minnesota Lynx @ New York Liberty</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9672,17 +9672,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5675711538461538</v>
+        <v>0.592854054054054</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-131</v>
+        <v>-146</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-108</v>
+        <v>-122</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx @ New York Liberty</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9738,17 +9738,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5889522522522523</v>
+        <v>0.3994074074074074</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-143</v>
+        <v>150</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-122</v>
+        <v>170</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 39.9% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9850,17 +9850,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9870,17 +9870,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4057414448669202</v>
+        <v>0.5483596153846154</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>146</v>
+        <v>-121</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>163</v>
+        <v>-108</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.54405</v>
+        <v>0.5437384615384615</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>-119</v>
@@ -9987,12 +9987,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -10002,17 +10002,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5498971563981042</v>
+        <v>0.6754652482269503</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-122</v>
+        <v>-208</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-111</v>
+        <v>-182</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10036,7 +10036,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 67.5% (fair -208). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10053,32 +10053,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Los Angeles Angels +1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4810599078341014</v>
+        <v>0.5640801843317972</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>108</v>
+        <v>-129</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>117</v>
+        <v>-117</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10119,32 +10119,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels +1.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5626783410138249</v>
+        <v>0.4804147465437788</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-129</v>
+        <v>108</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-117</v>
+        <v>117</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10180,17 +10180,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -10200,17 +10200,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.6766237762237762</v>
+        <v>0.4982211538461538</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-209</v>
+        <v>101</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-186</v>
+        <v>108</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 67.7% (fair -209). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10246,17 +10246,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Seattle Storm @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Phoenix Mercury</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4982211538461538</v>
+        <v>0.61854</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>101</v>
+        <v>-162</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>108</v>
+        <v>-150</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10312,37 +10312,37 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4656306306306307</v>
+        <v>0.5014705882352941</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>115</v>
+        <v>-101</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 50.1% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10375,141 +10375,9 @@
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>Phoenix Mercury</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="n">
-        <v>0.6166800000000001</v>
-      </c>
-      <c r="G25" s="14" t="n">
-        <v>-161</v>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v>-150</v>
-      </c>
-      <c r="I25" s="13">
-        <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
-        <v/>
-      </c>
-      <c r="J25" s="16">
-        <f>IF($H$25="","",$F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))</f>
-        <v/>
-      </c>
-      <c r="K25" s="17">
-        <f>IF($H$25="","",MAX(0,($F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))/IF($H$25&lt;0,-100/$H$25,$H$25/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L25" s="18">
-        <f>IF($H$25="","",ROUND(MIN($K$25,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M25" s="12">
-        <f>IF($J$25="","",IF($J$25&lt;0,"Pass",IF($J$25&lt;'Settings'!$B$4,"Thin",IF($J$25&lt;0.06,"✅ Sharp band",IF($J$25&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N25" s="19" t="inlineStr">
-        <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
-        </is>
-      </c>
-      <c r="O25" s="15" t="n"/>
-      <c r="P25" s="16">
-        <f>IF(OR($H$25="",$O$25=""),"",(1+IF($H$25&lt;0,-100/$H$25,$H$25/100))/(1+IF($O$25&lt;0,-100/$O$25,$O$25/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>23:40</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>0.4805633802816902</v>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>108</v>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>113</v>
-      </c>
-      <c r="I26" s="13">
-        <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
-        <v/>
-      </c>
-      <c r="J26" s="16">
-        <f>IF($H$26="","",$F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))</f>
-        <v/>
-      </c>
-      <c r="K26" s="17">
-        <f>IF($H$26="","",MAX(0,($F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))/IF($H$26&lt;0,-100/$H$26,$H$26/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L26" s="18">
-        <f>IF($H$26="","",ROUND(MIN($K$26,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M26" s="12">
-        <f>IF($J$26="","",IF($J$26&lt;0,"Pass",IF($J$26&lt;'Settings'!$B$4,"Thin",IF($J$26&lt;0.06,"✅ Sharp band",IF($J$26&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N26" s="19" t="inlineStr">
-        <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
-        </is>
-      </c>
-      <c r="O26" s="15" t="n"/>
-      <c r="P26" s="16">
-        <f>IF(OR($H$26="",$O$26=""),"",(1+IF($H$26&lt;0,-100/$H$26,$H$26/100))/(1+IF($O$26&lt;0,-100/$O$26,$O$26/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J26">
+  <conditionalFormatting sqref="J5:J24">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -11011,7 +10879,7 @@
         <v>-130</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-123</v>
+        <v>-124</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -11071,10 +10939,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3233916083916084</v>
+        <v>0.3245104895104895</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>186</v>
@@ -11101,7 +10969,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 32.3% (fair +209). Your call.</t>
+          <t>Model 32.5% (fair +208). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11137,13 +11005,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6766237762237762</v>
+        <v>0.6754652482269503</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-209</v>
+        <v>-208</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-186</v>
+        <v>-182</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -11167,7 +11035,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 67.7% (fair -209). Your call.</t>
+          <t>Model 67.5% (fair -208). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11199,17 +11067,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 7</t>
+          <t>Over 6.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5421</v>
+        <v>0.5667923076923076</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-118</v>
+        <v>-131</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>116</v>
+        <v>-108</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -11233,7 +11101,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11265,17 +11133,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 7</t>
+          <t>Under 6.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4579</v>
+        <v>0.4331904761904761</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -11299,7 +11167,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11335,13 +11203,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4853879310344827</v>
+        <v>0.5786</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>106</v>
+        <v>-137</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -11365,7 +11233,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 57.9% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11401,13 +11269,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5146017621145375</v>
+        <v>0.4214</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-106</v>
+        <v>137</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-127</v>
+        <v>119</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -11431,7 +11299,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 42.1% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11467,7 +11335,7 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5364746543778801</v>
+        <v>0.5363668202764977</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>-116</v>
@@ -11533,13 +11401,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4634883720930233</v>
+        <v>0.4636405529953917</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>116</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11563,7 +11431,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11599,13 +11467,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4248</v>
+        <v>0.4304</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11629,7 +11497,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 43.0% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11665,13 +11533,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5751999999999999</v>
+        <v>0.5696</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-135</v>
+        <v>-132</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11695,7 +11563,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 57.0% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11731,13 +11599,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5692304347826088</v>
+        <v>0.5656814977973569</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-132</v>
+        <v>-130</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-130</v>
+        <v>-127</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11761,7 +11629,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11797,13 +11665,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4307929515418502</v>
+        <v>0.4343555555555556</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11827,7 +11695,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11863,13 +11731,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5498971563981042</v>
+        <v>0.5483596153846154</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-122</v>
+        <v>-121</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11893,7 +11761,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11929,10 +11797,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4500961538461539</v>
+        <v>0.4516826923076923</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>108</v>
@@ -11959,7 +11827,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11995,7 +11863,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5252</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>-111</v>
@@ -12025,7 +11893,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -111). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12061,13 +11929,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4748</v>
+        <v>0.4733000000000001</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>111</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -12091,7 +11959,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +111). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12127,10 +11995,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4965196078431372</v>
+        <v>0.4995098039215686</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>104</v>
@@ -12157,7 +12025,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12193,13 +12061,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5034461538461539</v>
+        <v>0.5004745098039215</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-101</v>
+        <v>-100</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12223,7 +12091,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 50.0% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12331,7 +12199,7 @@
         <v>-146</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12397,7 +12265,7 @@
         <v>185</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12523,13 +12391,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5194384615384615</v>
+        <v>0.5271018518518519</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-108</v>
+        <v>-111</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-108</v>
+        <v>-116</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12553,7 +12421,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12589,13 +12457,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4805633802816902</v>
+        <v>0.4728837209302326</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -12619,7 +12487,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12655,10 +12523,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.5201</v>
+        <v>0.5014705882352941</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-108</v>
+        <v>-101</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>104</v>
@@ -12685,7 +12553,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 50.1% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12721,13 +12589,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.4799</v>
+        <v>0.49855</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12751,7 +12619,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 49.9% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12787,10 +12655,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5912666666666666</v>
+        <v>0.5865416666666666</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-145</v>
+        <v>-142</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>-140</v>
@@ -12817,7 +12685,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12853,13 +12721,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4087394957983194</v>
+        <v>0.4134334763948498</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12883,7 +12751,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +145). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12919,7 +12787,7 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4810599078341014</v>
+        <v>0.4804147465437788</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>108</v>
@@ -12949,7 +12817,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12985,13 +12853,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5189388888888889</v>
+        <v>0.5195986175115207</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>-108</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-116</v>
+        <v>-117</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -13015,7 +12883,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13047,17 +12915,17 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5573176470588235</v>
+        <v>0.5662</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-126</v>
+        <v>-131</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>-104</v>
+        <v>116</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -13081,7 +12949,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13113,14 +12981,14 @@
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4426960784313725</v>
+        <v>0.4338</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>104</v>
@@ -13147,7 +13015,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13255,7 +13123,7 @@
         <v>-186</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-132</v>
+        <v>164</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13315,7 +13183,7 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3832993197278912</v>
+        <v>0.3836734693877552</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>161</v>
@@ -13345,7 +13213,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 38.4% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13381,7 +13249,7 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.616708843537415</v>
+        <v>0.616312925170068</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>-161</v>
@@ -13411,7 +13279,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 61.6% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13447,13 +13315,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4879411764705882</v>
+        <v>0.4867475728155339</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>105</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13477,7 +13345,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13513,7 +13381,7 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5120470588235294</v>
+        <v>0.513270588235294</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>-105</v>
@@ -13543,7 +13411,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13579,7 +13447,7 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4373239436619719</v>
+        <v>0.4359154929577465</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>129</v>
@@ -13609,7 +13477,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13645,7 +13513,7 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5626783410138249</v>
+        <v>0.5640801843317972</v>
       </c>
       <c r="G50" s="14" t="n">
         <v>-129</v>
@@ -13675,7 +13543,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13711,13 +13579,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.3985614035087719</v>
+        <v>0.403525179856115</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13741,7 +13609,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 40.4% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13777,13 +13645,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.6014571428571428</v>
+        <v>0.5964920863309352</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-151</v>
+        <v>-148</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>-180</v>
+        <v>-178</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13807,7 +13675,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -151). Your call.</t>
+          <t>Model 59.6% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13843,13 +13711,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4602</v>
+        <v>0.4477</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13873,7 +13741,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13909,10 +13777,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5398000000000001</v>
+        <v>0.5523</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-117</v>
+        <v>-123</v>
       </c>
       <c r="H54" s="15" t="n">
         <v>117</v>
@@ -13939,7 +13807,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13975,13 +13843,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.3856</v>
+        <v>0.3818</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -14005,7 +13873,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -14041,10 +13909,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.6144000000000001</v>
+        <v>0.6182000000000001</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-159</v>
+        <v>-162</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>126</v>
@@ -14071,7 +13939,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14107,7 +13975,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4559447004608295</v>
+        <v>0.4562672811059908</v>
       </c>
       <c r="G57" s="14" t="n">
         <v>119</v>
@@ -14173,7 +14041,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.54405</v>
+        <v>0.5437384615384615</v>
       </c>
       <c r="G58" s="14" t="n">
         <v>-119</v>
@@ -14371,13 +14239,13 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4057414448669202</v>
+        <v>0.3994074074074074</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14401,7 +14269,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 39.9% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14437,13 +14305,13 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5942510791366906</v>
+        <v>0.6005979020979021</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-146</v>
+        <v>-150</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-178</v>
+        <v>-186</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14467,7 +14335,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 60.1% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14635,13 +14503,13 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4656306306306307</v>
+        <v>0.4693087557603687</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -14665,7 +14533,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14701,10 +14569,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5343819819819819</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-115</v>
+        <v>-113</v>
       </c>
       <c r="H66" s="15" t="n">
         <v>-122</v>
@@ -14731,7 +14599,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14767,7 +14635,7 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.4762660944206008</v>
+        <v>0.4759656652360515</v>
       </c>
       <c r="G67" s="14" t="n">
         <v>110</v>
@@ -14833,7 +14701,7 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5237231759656652</v>
+        <v>0.5240085836909871</v>
       </c>
       <c r="G68" s="14" t="n">
         <v>-110</v>
@@ -14899,10 +14767,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.5046</v>
+        <v>0.5068</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="H69" s="15" t="n">
         <v>-117</v>
@@ -14929,7 +14797,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14965,13 +14833,13 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4955</v>
+        <v>0.4932</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H70" s="15" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
@@ -14995,7 +14863,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -15031,10 +14899,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.5059903846153846</v>
+        <v>0.5123769230769231</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-102</v>
+        <v>-105</v>
       </c>
       <c r="H71" s="15" t="n">
         <v>-108</v>
@@ -15061,7 +14929,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15097,13 +14965,13 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.4939999999999999</v>
+        <v>0.4876470588235294</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -15127,7 +14995,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15169,7 +15037,7 @@
         <v>102</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -15952,13 +15820,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6588395604395604</v>
+        <v>0.6616490196078432</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-193</v>
+        <v>-196</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-264</v>
+        <v>-257</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -15982,7 +15850,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 65.9% (fair -193). Your call.</t>
+          <t>Model 66.2% (fair -196). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -16018,13 +15886,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3411484593837535</v>
+        <v>0.3383243243243243</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -16048,7 +15916,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 34.1% (fair +193). Your call.</t>
+          <t>Model 33.8% (fair +196). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -16084,13 +15952,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6154460093896714</v>
+        <v>0.6154326923076923</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-160</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -16156,7 +16024,7 @@
         <v>160</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -16222,7 +16090,7 @@
         <v>-153</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -16288,7 +16156,7 @@
         <v>153</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -16348,13 +16216,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.7072282051282052</v>
+        <v>0.7060928381962864</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-242</v>
+        <v>-240</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-290</v>
+        <v>-277</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -16378,7 +16246,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 70.7% (fair -242). Your call.</t>
+          <t>Model 70.6% (fair -240). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -16414,10 +16282,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.29275</v>
+        <v>0.293875</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>300</v>
@@ -16444,7 +16312,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 29.3% (fair +242). Your call.</t>
+          <t>Model 29.4% (fair +240). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -16480,13 +16348,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4191176470588235</v>
+        <v>0.4191346153846154</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>139</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -16552,7 +16420,7 @@
         <v>-139</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -16618,7 +16486,7 @@
         <v>-114</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -16684,7 +16552,7 @@
         <v>114</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -16744,13 +16612,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.3833203125</v>
+        <v>0.3814615384615385</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -16774,7 +16642,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 38.1% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -16810,10 +16678,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6166800000000001</v>
+        <v>0.61854</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-161</v>
+        <v>-162</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>-150</v>
@@ -16840,7 +16708,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -16872,17 +16740,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 169</t>
+          <t>Over 168</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5351415094339622</v>
+        <v>0.5584752475247525</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-115</v>
+        <v>-126</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>112</v>
+        <v>-102</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -16906,7 +16774,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -16938,17 +16806,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 169</t>
+          <t>Under 168</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4648</v>
+        <v>0.4415</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>112</v>
+        <v>-102</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -16972,7 +16840,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -17014,7 +16882,7 @@
         <v>105</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -17140,10 +17008,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5889522522522523</v>
+        <v>0.592854054054054</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-143</v>
+        <v>-146</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>-122</v>
@@ -17170,7 +17038,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -17206,13 +17074,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4110454545454545</v>
+        <v>0.4071806167400881</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -17236,7 +17104,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -17668,13 +17536,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5206666666666666</v>
+        <v>0.5206326923076923</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>-109</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -17740,7 +17608,7 @@
         <v>109</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -17800,10 +17668,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5085</v>
+        <v>0.50605</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-103</v>
+        <v>-102</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>100</v>
@@ -17830,7 +17698,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -17866,13 +17734,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4915</v>
+        <v>0.4939490196078431</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -17896,7 +17764,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +103). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>

--- a/data/output/workbook/2026-07-02.xlsx
+++ b/data/output/workbook/2026-07-02.xlsx
@@ -431,7 +431,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10506075"/>
+    <ext cx="10125075" cy="10353675"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -521,7 +521,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10734675"/>
+    <ext cx="10125075" cy="10582275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10277475"/>
+    <ext cx="10125075" cy="10696575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02 08:14</t>
+          <t>2026-07-02 11:16</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,174 +1175,249 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>Miami Marlins offense vs Colorado Rockies defense</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
-        <is>
-          <t>Miami Marlins offense vs Colorado Rockies defense</t>
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E67" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F67" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H67" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I67" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J67" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K67" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L67" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M67" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N67" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O67" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P67" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q67" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B68" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C68" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D68" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E68" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F68" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G68" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H68" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I68" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J68" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K68" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L68" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M68" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N68" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O68" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P68" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q68" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>4.526</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H68" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J68" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>6.567</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>5.697</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>4.526</v>
+        <v>8.286</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>4.833</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J69" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>5.85</v>
+        <v>7.8</v>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O69" s="32" t="n">
-        <v>6.567</v>
+        <v>12.6</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>5.697</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>8.286</v>
+        <v>0.918</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>7.8</v>
+        <v>1.6</v>
       </c>
       <c r="D70" s="32" t="inlineStr">
         <is>
@@ -1395,29 +1470,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O70" s="32" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>9.779999999999999</v>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>0.918</v>
+        <v>7.816</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -1470,320 +1549,316 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O71" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>7.28</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.816</v>
+        <v>0.527</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.3</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H72" s="36" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J72" s="36" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>0.75</v>
       </c>
       <c r="O72" s="32" t="n">
-        <v>6.8</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.28</v>
+        <v>0.68</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H73" s="36" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="36" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>Colorado Rockies offense vs Miami Marlins defense</t>
+        </is>
+      </c>
+    </row>
     <row r="75">
-      <c r="A75" s="29" t="inlineStr">
-        <is>
-          <t>Colorado Rockies offense vs Miami Marlins defense</t>
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C75" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D75" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E75" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F75" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G75" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H75" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I75" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J75" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K75" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L75" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M75" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N75" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O75" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P75" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q75" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B76" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C76" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D76" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E76" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F76" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G76" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H76" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I76" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J76" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K76" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L76" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M76" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N76" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O76" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P76" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q76" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>4.658</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H76" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>4.184</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>4.658</v>
+        <v>8.32</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
+        <v>11.8</v>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>3.15</v>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>3.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>4.184</v>
+        <v>7.694</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>8.32</v>
+        <v>0.92</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>11.8</v>
+        <v>2</v>
       </c>
       <c r="D78" s="32" t="inlineStr">
         <is>
@@ -1836,29 +1911,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O78" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>7.694</v>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>0.92</v>
+        <v>8.92</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -1911,151 +1990,72 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O79" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>8.531000000000001</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.92</v>
+        <v>0.467</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.5</v>
+      </c>
+      <c r="D80" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E80" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F80" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G80" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H80" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
         </is>
       </c>
       <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J80" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L80" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M80" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N80" s="32" t="n">
+        <v>0.4</v>
       </c>
       <c r="O80" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.531000000000001</v>
+        <v>0.635</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="C81" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E81" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G81" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H81" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M81" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O81" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3906,7 +3906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3923,174 +3923,249 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays offense vs Kansas City Royals defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays offense vs Kansas City Royals defense</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.708</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>6.933</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.708</v>
+        <v>8.778</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>6.933</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>6.6</v>
+        <v>7</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>5.8</v>
+        <v>8.5</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>5.26</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.778</v>
+        <v>0.956</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -4143,29 +4218,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O71" s="32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>8.603999999999999</v>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>0.956</v>
+        <v>7.244</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -4218,324 +4297,320 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O72" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>8.208</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>7.244</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.7</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>1.25</v>
       </c>
       <c r="O73" s="32" t="n">
-        <v>9.5</v>
+        <v>1.067</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>8.208</v>
+        <v>0.838</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Kansas City Royals offense vs Tampa Bay Rays defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.156</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>4.967</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>1.067</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Kansas City Royals offense vs Tampa Bay Rays defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="K77" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.067</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.431</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.156</v>
+        <v>7.792</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>4.967</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>29th</t>
+        <v>9.25</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>3.067</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>3.45</v>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>4.133</v>
+        <v>10.8</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.431</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>7.792</v>
+        <v>0.896</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>9.25</v>
+        <v>1.25</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -4588,29 +4663,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O79" s="32" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="P79" s="32" t="n">
-        <v>8.467000000000001</v>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.896</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>1.25</v>
+        <v>9.25</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -4663,155 +4742,76 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O80" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>7.778</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8.021000000000001</v>
+        <v>0.459</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.8</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H81" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J81" s="36" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.35</v>
       </c>
       <c r="O81" s="32" t="n">
-        <v>7</v>
+        <v>0.533</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>7.778</v>
+        <v>0.486</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H82" s="36" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J82" s="36" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6670,7 +6670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6687,891 +6687,891 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>San Diego Padres offense vs Los Angeles Dodgers defense</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B66" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C66" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D66" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E66" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F66" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G66" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H66" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I66" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J66" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K66" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L66" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M66" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N66" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O66" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P66" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q66" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>4.013</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>3.967</v>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E67" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H67" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="36" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L67" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M67" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="N67" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>3.487</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>7.087</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>6.596</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>1.022</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>8.348000000000001</v>
+        <v>4.013</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.967</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>4.5</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>7.75</v>
+        <v>4.167</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>8.106</v>
+        <v>3.487</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>7.087</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>6.596</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8.348000000000001</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>8.106</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B71" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="C71" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="D71" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="E71" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="F71" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="G71" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H71" s="34" t="inlineStr">
+      <c r="H74" s="34" t="inlineStr">
         <is>
           <t>25th</t>
         </is>
       </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="33" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="33" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
       </c>
-      <c r="K71" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L71" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M71" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N71" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="O71" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P71" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.452</v>
       </c>
-      <c r="Q71" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Los Angeles Dodgers offense vs San Diego Padres defense</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B74" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C74" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D74" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E74" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F74" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G74" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H74" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I74" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J74" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K74" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L74" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M74" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N74" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O74" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P74" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q74" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>5.474</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>4.177</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>9.191000000000001</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>7.848</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>1.553</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>8.510999999999999</v>
+        <v>5.474</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.333</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>5.4</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>5.5</v>
+        <v>5.133</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>8.304</v>
+        <v>4.177</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>9.191000000000001</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>7.848</v>
+      </c>
+      <c r="Q79" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>8.510999999999999</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>8.304</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B79" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.658</v>
       </c>
-      <c r="C79" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="D79" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="E79" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="F79" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G79" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H79" s="36" t="inlineStr">
+      <c r="H82" s="36" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="I79" s="32" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="J79" s="34" t="inlineStr">
+      <c r="J82" s="34" t="inlineStr">
         <is>
           <t>26th</t>
         </is>
       </c>
-      <c r="K79" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="L79" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M79" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="N79" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="O79" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="P79" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q79" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8938,7 +8938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9073,22 +9073,22 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Over 167.5</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6154326923076923</v>
+        <v>0.3351458885941645</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-160</v>
+        <v>198</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>108</v>
+        <v>277</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 61.5% (fair -160). Your call.</t>
+          <t>Model 33.5% (fair +198). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9139,22 +9139,22 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Washington Mystics</t>
+          <t>Over 167.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3383243243243243</v>
+        <v>0.6154352941176471</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>196</v>
+        <v>-160</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>270</v>
+        <v>-104</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 33.8% (fair +196). Your call.</t>
+          <t>Model 61.5% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9214,13 +9214,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.293875</v>
+        <v>0.2968311688311688</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 29.4% (fair +240). Your call.</t>
+          <t>Model 29.7% (fair +237). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9280,13 +9280,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3836734693877552</v>
+        <v>0.3823986486486486</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +161). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9322,17 +9322,17 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9342,17 +9342,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.403525179856115</v>
+        <v>0.4742436974789916</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +148). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9408,17 +9408,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4759656652360515</v>
+        <v>0.56145</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>110</v>
+        <v>-128</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9459,32 +9459,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Over 168</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5584752475247525</v>
+        <v>0.4028776978417266</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-126</v>
+        <v>148</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-102</v>
+        <v>178</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 40.3% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9520,37 +9520,37 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>Seattle Storm @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Over 169</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5675711538461538</v>
+        <v>0.5351674641148326</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-131</v>
+        <v>-115</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-108</v>
+        <v>109</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9586,37 +9586,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 6.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5667923076923076</v>
+        <v>0.429296875</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-131</v>
+        <v>133</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-108</v>
+        <v>156</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9657,12 +9657,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx @ New York Liberty</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9672,17 +9672,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.592854054054054</v>
+        <v>0.4937387387387388</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-146</v>
+        <v>103</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-122</v>
+        <v>122</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 49.4% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9718,17 +9718,17 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9738,17 +9738,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3994074074074074</v>
+        <v>0.5320792079207921</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>150</v>
+        <v>-114</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +150). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9799,22 +9799,22 @@
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -1.5</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.546819512195122</v>
+        <v>0.5900513513513514</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-121</v>
+        <v>-144</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-105</v>
+        <v>-122</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9850,37 +9850,37 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Minnesota Lynx @ New York Liberty</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Minnesota Lynx -1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5483596153846154</v>
+        <v>0.5462039215686274</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-121</v>
+        <v>-120</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9921,12 +9921,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9936,17 +9936,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5437384615384615</v>
+        <v>0.3957037037037037</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-119</v>
+        <v>153</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-108</v>
+        <v>170</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 39.6% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9987,32 +9987,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Los Angeles Angels +1.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.6754652482269503</v>
+        <v>0.5620558139534884</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-208</v>
+        <v>-128</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-182</v>
+        <v>-115</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10036,7 +10036,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 67.5% (fair -208). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -10068,17 +10068,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels +1.5</t>
+          <t>San Diego Padres +1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5640801843317972</v>
+        <v>0.5612</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-129</v>
+        <v>-128</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-117</v>
+        <v>-115</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10114,17 +10114,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -10134,17 +10134,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4804147465437788</v>
+        <v>0.5410384615384616</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>108</v>
+        <v>-118</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>117</v>
+        <v>-108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -10180,17 +10180,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -10200,17 +10200,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4982211538461538</v>
+        <v>0.6705602836879432</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>101</v>
+        <v>-204</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>108</v>
+        <v>-182</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 67.1% (fair -204). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10246,12 +10246,12 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>Chicago Sky @ Las Vegas Aces</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -10261,22 +10261,22 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>Over 183.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.61854</v>
+        <v>0.4971634615384615</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-162</v>
+        <v>101</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-150</v>
+        <v>108</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10312,37 +10312,37 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5014705882352941</v>
+        <v>0.4656306306306307</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-101</v>
+        <v>115</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -101). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10375,9 +10375,141 @@
         <v/>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.4727649769585254</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>117</v>
+      </c>
+      <c r="I25" s="13">
+        <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="16">
+        <f>IF($H$25="","",$F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>IF($H$25="","",MAX(0,($F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))/IF($H$25&lt;0,-100/$H$25,$H$25/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L25" s="18">
+        <f>IF($H$25="","",ROUND(MIN($K$25,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M25" s="12">
+        <f>IF($J$25="","",IF($J$25&lt;0,"Pass",IF($J$25&lt;'Settings'!$B$4,"Thin",IF($J$25&lt;0.06,"✅ Sharp band",IF($J$25&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="19" t="inlineStr">
+        <is>
+          <t>Model 47.3% (fair +112). Your call.</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="n"/>
+      <c r="P25" s="16">
+        <f>IF(OR($H$25="",$O$25=""),"",(1+IF($H$25&lt;0,-100/$H$25,$H$25/100))/(1+IF($O$25&lt;0,-100/$O$25,$O$25/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.4953883495145631</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>102</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>106</v>
+      </c>
+      <c r="I26" s="13">
+        <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="16">
+        <f>IF($H$26="","",$F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="17">
+        <f>IF($H$26="","",MAX(0,($F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))/IF($H$26&lt;0,-100/$H$26,$H$26/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L26" s="18">
+        <f>IF($H$26="","",ROUND(MIN($K$26,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M26" s="12">
+        <f>IF($J$26="","",IF($J$26&lt;0,"Pass",IF($J$26&lt;'Settings'!$B$4,"Thin",IF($J$26&lt;0.06,"✅ Sharp band",IF($J$26&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.5% (fair +102). Your call.</t>
+        </is>
+      </c>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="16">
+        <f>IF(OR($H$26="",$O$26=""),"",(1+IF($H$26&lt;0,-100/$H$26,$H$26/100))/(1+IF($O$26&lt;0,-100/$O$26,$O$26/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J24">
+  <conditionalFormatting sqref="J5:J26">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -10399,7 +10531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P82"/>
+  <dimension ref="A1:P78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10543,13 +10675,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4548387096774194</v>
+        <v>0.4522018348623854</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -10573,7 +10705,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10609,13 +10741,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5451552995391705</v>
+        <v>0.5478</v>
       </c>
       <c r="G6" s="14" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H6" s="15" t="n">
         <v>-120</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>-117</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10639,7 +10771,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10671,17 +10803,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5295</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-113</v>
+        <v>-149</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10705,7 +10837,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -113). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10737,17 +10869,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4705</v>
+        <v>0.4016999999999999</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10771,7 +10903,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +113). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10813,7 +10945,7 @@
         <v>130</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -10879,7 +11011,7 @@
         <v>-130</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-124</v>
+        <v>-117</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -10939,13 +11071,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3245104895104895</v>
+        <v>0.3294604316546763</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -10969,7 +11101,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 32.5% (fair +208). Your call.</t>
+          <t>Model 32.9% (fair +204). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11005,10 +11137,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6754652482269503</v>
+        <v>0.6705602836879432</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-208</v>
+        <v>-204</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-182</v>
@@ -11035,7 +11167,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 67.5% (fair -208). Your call.</t>
+          <t>Model 67.1% (fair -204). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11067,17 +11199,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 6.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5667923076923076</v>
+        <v>0.5392</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-131</v>
+        <v>-117</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-108</v>
+        <v>129</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -11101,7 +11233,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11133,17 +11265,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 6.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4331904761904761</v>
+        <v>0.4608</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -11167,7 +11299,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11203,10 +11335,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5786</v>
+        <v>0.5746</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-137</v>
+        <v>-135</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>125</v>
@@ -11233,7 +11365,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -137). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11269,13 +11401,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4214</v>
+        <v>0.4254</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -11299,7 +11431,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +137). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11335,13 +11467,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5363668202764977</v>
+        <v>0.5478343612334802</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-116</v>
+        <v>-121</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-117</v>
+        <v>-127</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11365,7 +11497,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -116). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11401,13 +11533,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4636405529953917</v>
+        <v>0.4521777777777778</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11431,7 +11563,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11467,10 +11599,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4304</v>
+        <v>0.4198</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>111</v>
@@ -11497,7 +11629,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +132). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11533,10 +11665,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5696</v>
+        <v>0.5802</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-132</v>
+        <v>-138</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>105</v>
@@ -11563,7 +11695,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -132). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11580,32 +11712,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies +1.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5656814977973569</v>
+        <v>0.5320792079207921</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-130</v>
+        <v>-114</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-127</v>
+        <v>102</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11629,7 +11761,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -130). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11646,32 +11778,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins -1.5</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4343555555555556</v>
+        <v>0.4679376237623762</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>125</v>
+        <v>-102</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11695,7 +11827,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +130). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11722,22 +11854,22 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5483596153846154</v>
+        <v>0.5252</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-121</v>
+        <v>-111</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-108</v>
+        <v>104</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11761,7 +11893,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 52.5% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11788,22 +11920,22 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4516826923076923</v>
+        <v>0.4748</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11827,7 +11959,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 47.5% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11844,32 +11976,32 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.4953883495145631</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-111</v>
+        <v>102</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11893,7 +12025,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11910,32 +12042,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4733000000000001</v>
+        <v>0.5045884615384615</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>111</v>
+        <v>-102</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>106</v>
+        <v>-108</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11959,7 +12091,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11986,22 +12118,22 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4995098039215686</v>
+        <v>0.4042</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -12025,7 +12157,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 40.4% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12052,22 +12184,22 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5004745098039215</v>
+        <v>0.5958</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-100</v>
+        <v>-147</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-104</v>
+        <v>108</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12091,7 +12223,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair -100). Your call.</t>
+          <t>Model 59.6% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12118,22 +12250,22 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Atlanta Braves -1.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4072</v>
+        <v>0.3473</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12157,7 +12289,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 34.7% (fair +188). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12184,22 +12316,22 @@
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5928</v>
+        <v>0.6527000000000001</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-146</v>
+        <v>-188</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12223,7 +12355,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 65.3% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12240,32 +12372,32 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves -1.5</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.3508</v>
+        <v>0.5272348837209303</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>185</v>
+        <v>-112</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>175</v>
+        <v>-115</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12289,7 +12421,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 35.1% (fair +185). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12306,32 +12438,32 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals +1.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6492</v>
+        <v>0.4727649769585254</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-185</v>
+        <v>112</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12355,7 +12487,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 64.9% (fair -185). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12382,22 +12514,22 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Over 11</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5271018518518519</v>
+        <v>0.4289</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-111</v>
+        <v>133</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-116</v>
+        <v>117</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12421,7 +12553,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12448,22 +12580,22 @@
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Under 11</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4728837209302326</v>
+        <v>0.5710999999999999</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>111</v>
+        <v>-133</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -12487,7 +12619,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12504,29 +12636,29 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.5014705882352941</v>
+        <v>0.4984313725490195</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-101</v>
+        <v>101</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>104</v>
@@ -12553,7 +12685,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -101). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12570,32 +12702,32 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.49855</v>
+        <v>0.5015961165048544</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>101</v>
+        <v>-101</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12619,7 +12751,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12636,32 +12768,32 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5865416666666666</v>
+        <v>0.6417</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-142</v>
+        <v>-179</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-140</v>
+        <v>113</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12685,7 +12817,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 64.2% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12702,32 +12834,32 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays -1.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4134334763948498</v>
+        <v>0.3583</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12751,7 +12883,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 35.8% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12778,22 +12910,22 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Texas Rangers -1.5</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4804147465437788</v>
+        <v>0.3529</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12817,7 +12949,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 35.3% (fair +183). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12844,22 +12976,22 @@
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Detroit Tigers +1.5</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5195986175115207</v>
+        <v>0.6471</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-108</v>
+        <v>-183</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-117</v>
+        <v>178</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12883,7 +13015,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 64.7% (fair -183). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12900,32 +13032,32 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5662</v>
+        <v>0.3823986486486486</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-131</v>
+        <v>162</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>116</v>
+        <v>196</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12949,7 +13081,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12966,32 +13098,32 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4338</v>
+        <v>0.6175872483221476</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>131</v>
+        <v>-161</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>104</v>
+        <v>-198</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -13015,7 +13147,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 61.8% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13032,32 +13164,32 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers -1.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.3501</v>
+        <v>0.495</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>186</v>
+        <v>102</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -13081,7 +13213,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 35.0% (fair +186). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13098,32 +13230,32 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers +1.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.6498999999999999</v>
+        <v>0.505</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-186</v>
+        <v>-102</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>164</v>
+        <v>105</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13147,7 +13279,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 65.0% (fair -186). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13174,22 +13306,22 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Seattle Mariners -1.5</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.3836734693877552</v>
+        <v>0.4379439252336449</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>194</v>
+        <v>114</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13213,7 +13345,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +161). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13240,22 +13372,22 @@
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Los Angeles Angels +1.5</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.616312925170068</v>
+        <v>0.5620558139534884</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-161</v>
+        <v>-128</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-194</v>
+        <v>-115</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13279,7 +13411,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -161). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13296,32 +13428,32 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4867475728155339</v>
+        <v>0.4028776978417266</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13345,7 +13477,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 40.3% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13362,32 +13494,32 @@
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.513270588235294</v>
+        <v>0.5971323741007194</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-105</v>
+        <v>-148</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-104</v>
+        <v>-178</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13411,7 +13543,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13428,32 +13560,32 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners -1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4359154929577465</v>
+        <v>0.4602</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13477,7 +13609,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13494,32 +13626,32 @@
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels +1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5640801843317972</v>
+        <v>0.5398000000000001</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-129</v>
+        <v>-117</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-117</v>
+        <v>105</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13543,7 +13675,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13570,22 +13702,22 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Los Angeles Dodgers -1.5</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.403525179856115</v>
+        <v>0.4388262910798122</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13609,7 +13741,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +148). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13636,22 +13768,22 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>San Diego Padres +1.5</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5964920863309352</v>
+        <v>0.5612</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-148</v>
+        <v>-128</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>-178</v>
+        <v>-115</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13675,7 +13807,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -148). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13687,37 +13819,37 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4477</v>
+        <v>0.4589671361502348</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13741,7 +13873,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13753,37 +13885,37 @@
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5523</v>
+        <v>0.5410384615384616</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-123</v>
+        <v>-118</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>117</v>
+        <v>-108</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13807,7 +13939,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13819,37 +13951,37 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers -1.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.3818</v>
+        <v>0.4937387387387388</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13873,7 +14005,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 38.2% (fair +162). Your call.</t>
+          <t>Model 49.4% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13885,37 +14017,37 @@
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres +1.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.6182000000000001</v>
+        <v>0.5062718309859155</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-162</v>
+        <v>-103</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>126</v>
+        <v>-113</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13939,7 +14071,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -162). Your call.</t>
+          <t>Model 50.6% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13956,12 +14088,12 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -13971,17 +14103,17 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4562672811059908</v>
+        <v>0.3957037037037037</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -14005,7 +14137,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 39.6% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14022,12 +14154,12 @@
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -14037,17 +14169,17 @@
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5437384615384615</v>
+        <v>0.6043333333333333</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-119</v>
+        <v>-153</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-108</v>
+        <v>-200</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -14071,7 +14203,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 60.4% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14088,12 +14220,12 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -14103,17 +14235,17 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4982211538461538</v>
+        <v>0.56145</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>101</v>
+        <v>-128</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14137,7 +14269,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14154,12 +14286,12 @@
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -14169,17 +14301,17 @@
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5017326923076924</v>
+        <v>0.4385576923076923</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-101</v>
+        <v>128</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>-108</v>
+        <v>108</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -14203,7 +14335,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14220,12 +14352,12 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -14235,17 +14367,17 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.3994074074074074</v>
+        <v>0.4656306306306307</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14269,7 +14401,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +150). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14286,12 +14418,12 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
@@ -14301,17 +14433,17 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.6005979020979021</v>
+        <v>0.5343819819819819</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-150</v>
+        <v>-115</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>-186</v>
+        <v>-122</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14335,7 +14467,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -150). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14352,12 +14484,12 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -14367,17 +14499,17 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.5675711538461538</v>
+        <v>0.4742436974789916</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-131</v>
+        <v>111</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>-108</v>
+        <v>138</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -14401,7 +14533,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14418,12 +14550,12 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -14433,17 +14565,17 @@
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.432451923076923</v>
+        <v>0.5257210300429185</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>131</v>
+        <v>-111</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>108</v>
+        <v>-133</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -14467,7 +14599,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +131). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14484,12 +14616,12 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -14499,17 +14631,17 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4693087557603687</v>
+        <v>0.5706600000000001</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>113</v>
+        <v>-133</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>117</v>
+        <v>-150</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -14533,7 +14665,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14550,12 +14682,12 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -14565,17 +14697,17 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.429296875</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-113</v>
+        <v>133</v>
       </c>
       <c r="H66" s="15" t="n">
-        <v>-122</v>
+        <v>156</v>
       </c>
       <c r="I66" s="13">
         <f>IF($H$66="","",IF($H$66&lt;0,-$H$66/(-$H$66+100),100/($H$66+100)))</f>
@@ -14599,7 +14731,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14616,12 +14748,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -14631,17 +14763,17 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.4759656652360515</v>
+        <v>0.5095999999999999</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>110</v>
+        <v>-104</v>
       </c>
       <c r="H67" s="15" t="n">
-        <v>133</v>
+        <v>-104</v>
       </c>
       <c r="I67" s="13">
         <f>IF($H$67="","",IF($H$67&lt;0,-$H$67/(-$H$67+100),100/($H$67+100)))</f>
@@ -14665,7 +14797,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14682,12 +14814,12 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Houston Astros</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -14697,17 +14829,17 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5240085836909871</v>
+        <v>0.4903921568627451</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-110</v>
+        <v>104</v>
       </c>
       <c r="H68" s="15" t="n">
-        <v>-133</v>
+        <v>104</v>
       </c>
       <c r="I68" s="13">
         <f>IF($H$68="","",IF($H$68&lt;0,-$H$68/(-$H$68+100),100/($H$68+100)))</f>
@@ -14731,7 +14863,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14748,12 +14880,12 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -14763,17 +14895,17 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.5068</v>
+        <v>0.4907</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>-103</v>
+        <v>104</v>
       </c>
       <c r="H69" s="15" t="n">
-        <v>-117</v>
+        <v>122</v>
       </c>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
@@ -14797,7 +14929,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14814,12 +14946,12 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Boston Red Sox @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>01:38</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -14829,17 +14961,17 @@
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4932</v>
+        <v>0.5093</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>103</v>
+        <v>-104</v>
       </c>
       <c r="H70" s="15" t="n">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
@@ -14863,7 +14995,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14880,12 +15012,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -14895,17 +15027,17 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.5123769230769231</v>
+        <v>0.471924882629108</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-105</v>
+        <v>112</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>-108</v>
+        <v>113</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -14929,7 +15061,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14946,12 +15078,12 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Houston Astros</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -14961,17 +15093,17 @@
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.4876470588235294</v>
+        <v>0.5280760563380281</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>105</v>
+        <v>-112</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>104</v>
+        <v>-113</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -14995,7 +15127,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15012,12 +15144,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -15027,18 +15159,16 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4948</v>
+        <v>0.6686</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>102</v>
-      </c>
-      <c r="H73" s="15" t="n">
-        <v>117</v>
-      </c>
+        <v>-202</v>
+      </c>
+      <c r="H73" s="15" t="n"/>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
         <v/>
@@ -15061,7 +15191,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 66.9% (fair -202). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15078,12 +15208,12 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Los Angeles Angels</t>
+          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>01:38</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -15093,18 +15223,16 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5052</v>
+        <v>0.3314</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-102</v>
-      </c>
-      <c r="H74" s="15" t="n">
-        <v>108</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="H74" s="15" t="n"/>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
         <v/>
@@ -15127,7 +15255,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 33.1% (fair +202). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15144,12 +15272,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -15159,18 +15287,16 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.471924882629108</v>
+        <v>0.4052</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>112</v>
-      </c>
-      <c r="H75" s="15" t="n">
-        <v>113</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="H75" s="15" t="n"/>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
         <v/>
@@ -15193,7 +15319,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15210,12 +15336,12 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -15225,18 +15351,16 @@
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5280760563380281</v>
+        <v>0.5948</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H76" s="15" t="n">
-        <v>-113</v>
-      </c>
+        <v>-147</v>
+      </c>
+      <c r="H76" s="15" t="n"/>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
         <v/>
@@ -15259,7 +15383,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15276,12 +15400,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -15291,14 +15415,14 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.5268</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-157</v>
+        <v>-111</v>
       </c>
       <c r="H77" s="15" t="n"/>
       <c r="I77" s="13">
@@ -15323,7 +15447,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -157). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15340,12 +15464,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -15355,14 +15479,14 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.3896</v>
+        <v>0.4733</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="H78" s="15" t="n"/>
       <c r="I78" s="13">
@@ -15387,7 +15511,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +157). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15396,265 +15520,9 @@
         <v/>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>02:10</t>
-        </is>
-      </c>
-      <c r="D79" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="F79" s="13" t="n">
-        <v>0.4045</v>
-      </c>
-      <c r="G79" s="14" t="n">
-        <v>147</v>
-      </c>
-      <c r="H79" s="15" t="n"/>
-      <c r="I79" s="13">
-        <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
-        <v/>
-      </c>
-      <c r="J79" s="16">
-        <f>IF($H$79="","",$F$79*IF($H$79&lt;0,-100/$H$79,$H$79/100)-(1-$F$79))</f>
-        <v/>
-      </c>
-      <c r="K79" s="17">
-        <f>IF($H$79="","",MAX(0,($F$79*IF($H$79&lt;0,-100/$H$79,$H$79/100)-(1-$F$79))/IF($H$79&lt;0,-100/$H$79,$H$79/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L79" s="18">
-        <f>IF($H$79="","",ROUND(MIN($K$79,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M79" s="12">
-        <f>IF($J$79="","",IF($J$79&lt;0,"Pass",IF($J$79&lt;'Settings'!$B$4,"Thin",IF($J$79&lt;0.06,"✅ Sharp band",IF($J$79&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N79" s="19" t="inlineStr">
-        <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
-        </is>
-      </c>
-      <c r="O79" s="15" t="n"/>
-      <c r="P79" s="16">
-        <f>IF(OR($H$79="",$O$79=""),"",(1+IF($H$79&lt;0,-100/$H$79,$H$79/100))/(1+IF($O$79&lt;0,-100/$O$79,$O$79/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B80" s="20" t="inlineStr">
-        <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="C80" s="20" t="inlineStr">
-        <is>
-          <t>02:10</t>
-        </is>
-      </c>
-      <c r="D80" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E80" s="20" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="F80" s="13" t="n">
-        <v>0.5955</v>
-      </c>
-      <c r="G80" s="14" t="n">
-        <v>-147</v>
-      </c>
-      <c r="H80" s="15" t="n"/>
-      <c r="I80" s="13">
-        <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
-        <v/>
-      </c>
-      <c r="J80" s="16">
-        <f>IF($H$80="","",$F$80*IF($H$80&lt;0,-100/$H$80,$H$80/100)-(1-$F$80))</f>
-        <v/>
-      </c>
-      <c r="K80" s="17">
-        <f>IF($H$80="","",MAX(0,($F$80*IF($H$80&lt;0,-100/$H$80,$H$80/100)-(1-$F$80))/IF($H$80&lt;0,-100/$H$80,$H$80/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L80" s="18">
-        <f>IF($H$80="","",ROUND(MIN($K$80,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M80" s="12">
-        <f>IF($J$80="","",IF($J$80&lt;0,"Pass",IF($J$80&lt;'Settings'!$B$4,"Thin",IF($J$80&lt;0.06,"✅ Sharp band",IF($J$80&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N80" s="19" t="inlineStr">
-        <is>
-          <t>Model 59.6% (fair -147). Your call.</t>
-        </is>
-      </c>
-      <c r="O80" s="15" t="n"/>
-      <c r="P80" s="16">
-        <f>IF(OR($H$80="",$O$80=""),"",(1+IF($H$80&lt;0,-100/$H$80,$H$80/100))/(1+IF($O$80&lt;0,-100/$O$80,$O$80/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>02:10</t>
-        </is>
-      </c>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E81" s="12" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays</t>
-        </is>
-      </c>
-      <c r="F81" s="13" t="n">
-        <v>0.5266</v>
-      </c>
-      <c r="G81" s="14" t="n">
-        <v>-111</v>
-      </c>
-      <c r="H81" s="15" t="n"/>
-      <c r="I81" s="13">
-        <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
-        <v/>
-      </c>
-      <c r="J81" s="16">
-        <f>IF($H$81="","",$F$81*IF($H$81&lt;0,-100/$H$81,$H$81/100)-(1-$F$81))</f>
-        <v/>
-      </c>
-      <c r="K81" s="17">
-        <f>IF($H$81="","",MAX(0,($F$81*IF($H$81&lt;0,-100/$H$81,$H$81/100)-(1-$F$81))/IF($H$81&lt;0,-100/$H$81,$H$81/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L81" s="18">
-        <f>IF($H$81="","",ROUND(MIN($K$81,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M81" s="12">
-        <f>IF($J$81="","",IF($J$81&lt;0,"Pass",IF($J$81&lt;'Settings'!$B$4,"Thin",IF($J$81&lt;0.06,"✅ Sharp band",IF($J$81&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N81" s="19" t="inlineStr">
-        <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
-        </is>
-      </c>
-      <c r="O81" s="15" t="n"/>
-      <c r="P81" s="16">
-        <f>IF(OR($H$81="",$O$81=""),"",(1+IF($H$81&lt;0,-100/$H$81,$H$81/100))/(1+IF($O$81&lt;0,-100/$O$81,$O$81/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B82" s="20" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="C82" s="20" t="inlineStr">
-        <is>
-          <t>02:10</t>
-        </is>
-      </c>
-      <c r="D82" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E82" s="20" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="F82" s="13" t="n">
-        <v>0.4734</v>
-      </c>
-      <c r="G82" s="14" t="n">
-        <v>111</v>
-      </c>
-      <c r="H82" s="15" t="n"/>
-      <c r="I82" s="13">
-        <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
-        <v/>
-      </c>
-      <c r="J82" s="16">
-        <f>IF($H$82="","",$F$82*IF($H$82&lt;0,-100/$H$82,$H$82/100)-(1-$F$82))</f>
-        <v/>
-      </c>
-      <c r="K82" s="17">
-        <f>IF($H$82="","",MAX(0,($F$82*IF($H$82&lt;0,-100/$H$82,$H$82/100)-(1-$F$82))/IF($H$82&lt;0,-100/$H$82,$H$82/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L82" s="18">
-        <f>IF($H$82="","",ROUND(MIN($K$82,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M82" s="12">
-        <f>IF($J$82="","",IF($J$82&lt;0,"Pass",IF($J$82&lt;'Settings'!$B$4,"Thin",IF($J$82&lt;0.06,"✅ Sharp band",IF($J$82&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N82" s="19" t="inlineStr">
-        <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
-        </is>
-      </c>
-      <c r="O82" s="15" t="n"/>
-      <c r="P82" s="16">
-        <f>IF(OR($H$82="",$O$82=""),"",(1+IF($H$82&lt;0,-100/$H$82,$H$82/100))/(1+IF($O$82&lt;0,-100/$O$82,$O$82/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J82">
+  <conditionalFormatting sqref="J5:J78">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -15820,13 +15688,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6616490196078432</v>
+        <v>0.6648567567567568</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-196</v>
+        <v>-198</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-257</v>
+        <v>-270</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -15850,7 +15718,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 66.2% (fair -196). Your call.</t>
+          <t>Model 66.5% (fair -198). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -15886,13 +15754,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3383243243243243</v>
+        <v>0.3351458885941645</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -15916,7 +15784,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 33.8% (fair +196). Your call.</t>
+          <t>Model 33.5% (fair +198). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -15952,13 +15820,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6154326923076923</v>
+        <v>0.6154352941176471</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-160</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -16024,7 +15892,7 @@
         <v>160</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -16090,7 +15958,7 @@
         <v>-153</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -16156,7 +16024,7 @@
         <v>153</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -16216,13 +16084,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.7060928381962864</v>
+        <v>0.7031727272727273</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-240</v>
+        <v>-237</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-277</v>
+        <v>-285</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -16246,7 +16114,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 70.6% (fair -240). Your call.</t>
+          <t>Model 70.3% (fair -237). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -16282,13 +16150,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.293875</v>
+        <v>0.2968311688311688</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -16312,7 +16180,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 29.4% (fair +240). Your call.</t>
+          <t>Model 29.7% (fair +237). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -16486,7 +16354,7 @@
         <v>-114</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -16552,7 +16420,7 @@
         <v>114</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -16612,10 +16480,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.3814615384615385</v>
+        <v>0.3796153846153846</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>160</v>
@@ -16642,7 +16510,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 38.0% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -16678,13 +16546,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.61854</v>
+        <v>0.6204046875</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-162</v>
+        <v>-163</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -16708,7 +16576,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -16740,17 +16608,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 168</t>
+          <t>Over 169</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5584752475247525</v>
+        <v>0.5351674641148326</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-126</v>
+        <v>-115</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-102</v>
+        <v>109</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -16774,7 +16642,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -16806,17 +16674,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 168</t>
+          <t>Under 169</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4415</v>
+        <v>0.4648</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-102</v>
+        <v>109</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -16840,7 +16708,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -17008,10 +16876,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.592854054054054</v>
+        <v>0.5900513513513514</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-146</v>
+        <v>-144</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>-122</v>
@@ -17038,7 +16906,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -17074,13 +16942,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4071806167400881</v>
+        <v>0.40990990990991</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -17104,7 +16972,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -17136,17 +17004,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 173.5</t>
+          <t>Over 175.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4111269230769231</v>
+        <v>0.3660576923076923</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-108</v>
+        <v>108</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -17170,7 +17038,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 36.6% (fair +173). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -17202,17 +17070,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 173.5</t>
+          <t>Under 175.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5889</v>
+        <v>0.634</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-143</v>
+        <v>-173</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-108</v>
+        <v>108</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -17236,7 +17104,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 63.4% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -17272,10 +17140,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4532178217821782</v>
+        <v>0.4537623762376237</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>102</v>
@@ -17302,7 +17170,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -17338,13 +17206,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.546819512195122</v>
+        <v>0.5462039215686274</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-121</v>
+        <v>-120</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -17368,7 +17236,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -17404,10 +17272,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.19518</v>
+        <v>0.19664</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>400</v>
@@ -17434,7 +17302,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 19.5% (fair +412). Your call.</t>
+          <t>Model 19.7% (fair +409). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -17470,13 +17338,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.80486463878327</v>
+        <v>0.8033508196721312</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-412</v>
+        <v>-409</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-426</v>
+        <v>-388</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -17500,7 +17368,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 80.5% (fair -412). Your call.</t>
+          <t>Model 80.3% (fair -409). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -17532,17 +17400,17 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 182.5</t>
+          <t>Over 183.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5206326923076923</v>
+        <v>0.4971634615384615</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-109</v>
+        <v>101</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-108</v>
+        <v>108</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -17566,7 +17434,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -17598,17 +17466,17 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 182.5</t>
+          <t>Under 183.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4794</v>
+        <v>0.5028</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>109</v>
+        <v>-101</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-108</v>
+        <v>108</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -17632,7 +17500,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -17668,13 +17536,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.50605</v>
+        <v>0.517</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-102</v>
+        <v>-107</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -17698,7 +17566,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -17734,13 +17602,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4939490196078431</v>
+        <v>0.483</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-104</v>
+        <v>113</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -17764,7 +17632,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>

--- a/data/output/workbook/2026-07-02.xlsx
+++ b/data/output/workbook/2026-07-02.xlsx
@@ -429,7 +429,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10429875"/>
+    <ext cx="10125075" cy="10658475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -489,7 +489,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10429875"/>
+    <ext cx="10125075" cy="10582275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -549,7 +549,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10344150"/>
+    <ext cx="10125075" cy="10763250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -579,7 +579,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10696575"/>
+    <ext cx="10125075" cy="10953750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -922,7 +922,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02 17:04</t>
+          <t>2026-07-02 18:17</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1143,324 +1143,174 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Chicago White Sox offense vs Cleveland Guardians defense</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E67" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F67" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G67" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H67" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I67" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J67" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K67" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L67" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M67" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N67" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O67" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P67" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q67" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>4.932</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H68" s="36" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J68" s="36" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>7.939</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>1.354</v>
+        <v>4.932</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.133</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H70" s="36" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>4.1</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>0.6</v>
+        <v>4.267</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>1.143</v>
+        <v>4.13</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>9.208</v>
+        <v>7.792</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>8.167</v>
+        <v>8.667</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -1514,390 +1364,390 @@
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>9.388</v>
+        <v>7.939</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>1.354</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>9.208</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>8.167</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>9.388</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.597</v>
       </c>
-      <c r="C72" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.633</v>
       </c>
-      <c r="D72" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="E72" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="F72" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G72" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H72" s="33" t="inlineStr">
+      <c r="H74" s="33" t="inlineStr">
         <is>
           <t>6th</t>
         </is>
       </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="33" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="33" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="K72" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L72" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="M72" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="N72" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O72" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.367</v>
       </c>
-      <c r="P72" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.365</v>
       </c>
-      <c r="Q72" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Cleveland Guardians offense vs Chicago White Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D75" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E75" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F75" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G75" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H75" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I75" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J75" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K75" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L75" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M75" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N75" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O75" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P75" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q75" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>3.922</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H76" s="36" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>4.716</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>7.735</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>7.854</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>0.959</v>
+        <v>3.922</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.6</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>4.15</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>0.5</v>
+        <v>4.167</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>1.062</v>
+        <v>4.716</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8</v>
+        <v>7.735</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -1951,75 +1801,225 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>7.333</v>
+        <v>6.667</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.938</v>
+        <v>7.854</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>7.938</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B80" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.514</v>
       </c>
-      <c r="C80" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.367</v>
       </c>
-      <c r="D80" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="E80" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="F80" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G80" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H80" s="36" t="inlineStr">
+      <c r="H82" s="36" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="I80" s="32" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J80" s="34" t="inlineStr">
+      <c r="J82" s="34" t="inlineStr">
         <is>
           <t>21st</t>
         </is>
       </c>
-      <c r="K80" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L80" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M80" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="N80" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="O80" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="P80" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.556</v>
       </c>
-      <c r="Q80" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -2942,7 +2942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2959,249 +2959,174 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>Tampa Bay Rays offense vs Kansas City Royals defense</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E67" s="30" t="inlineStr">
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F67" s="30" t="inlineStr">
+      <c r="F68" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G67" s="30" t="inlineStr">
+      <c r="G68" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H67" s="30" t="inlineStr">
+      <c r="H68" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I67" s="30" t="inlineStr">
+      <c r="I68" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J67" s="30" t="inlineStr">
+      <c r="J68" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K67" s="30" t="inlineStr">
+      <c r="K68" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L67" s="30" t="inlineStr">
+      <c r="L68" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M67" s="30" t="inlineStr">
+      <c r="M68" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N67" s="30" t="inlineStr">
+      <c r="N68" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O67" s="30" t="inlineStr">
+      <c r="O68" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P67" s="30" t="inlineStr">
+      <c r="P68" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q67" s="30" t="inlineStr">
+      <c r="Q68" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>4.708</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H68" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J68" s="34" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>6.933</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>8.778</v>
+        <v>4.708</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.467</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>6.933</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>6.6</v>
       </c>
       <c r="O69" s="32" t="n">
-        <v>8.5</v>
+        <v>5.8</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>8.603999999999999</v>
+        <v>5.26</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>0.956</v>
+        <v>8.778</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>1.4</v>
+        <v>7</v>
       </c>
       <c r="D70" s="32" t="inlineStr">
         <is>
@@ -3255,28 +3180,28 @@
         </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>1.25</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.244</v>
+        <v>0.956</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>8.4</v>
+        <v>1.4</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -3330,319 +3255,319 @@
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>8.208</v>
+        <v>1.25</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>7.244</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>8.208</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
+      <c r="B73" s="32" t="n">
         <v>0.5570000000000001</v>
       </c>
-      <c r="C72" s="32" t="n">
+      <c r="C73" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="D72" s="32" t="n">
+      <c r="D73" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="E72" s="32" t="n">
+      <c r="E73" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="F72" s="32" t="n">
+      <c r="F73" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="G72" s="32" t="n">
+      <c r="G73" s="32" t="n">
         <v>1.4</v>
       </c>
-      <c r="H72" s="33" t="inlineStr">
+      <c r="H73" s="33" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="I72" s="32" t="inlineStr">
+      <c r="I73" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J72" s="34" t="inlineStr">
+      <c r="J73" s="34" t="inlineStr">
         <is>
           <t>25th</t>
         </is>
       </c>
-      <c r="K72" s="32" t="n">
+      <c r="K73" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="L72" s="32" t="n">
+      <c r="L73" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="M72" s="32" t="n">
+      <c r="M73" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="N72" s="32" t="n">
+      <c r="N73" s="32" t="n">
         <v>1.25</v>
       </c>
-      <c r="O72" s="32" t="n">
+      <c r="O73" s="32" t="n">
         <v>1.067</v>
       </c>
-      <c r="P72" s="32" t="n">
+      <c r="P73" s="32" t="n">
         <v>0.838</v>
       </c>
-      <c r="Q72" s="35" t="inlineStr">
+      <c r="Q73" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>Kansas City Royals offense vs Tampa Bay Rays defense</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B76" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C76" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D75" s="30" t="inlineStr">
+      <c r="D76" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E75" s="30" t="inlineStr">
+      <c r="E76" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F75" s="30" t="inlineStr">
+      <c r="F76" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G75" s="30" t="inlineStr">
+      <c r="G76" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H75" s="30" t="inlineStr">
+      <c r="H76" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I75" s="30" t="inlineStr">
+      <c r="I76" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J75" s="30" t="inlineStr">
+      <c r="J76" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K75" s="30" t="inlineStr">
+      <c r="K76" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L75" s="30" t="inlineStr">
+      <c r="L76" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M75" s="30" t="inlineStr">
+      <c r="M76" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N75" s="30" t="inlineStr">
+      <c r="N76" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O75" s="30" t="inlineStr">
+      <c r="O76" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P75" s="30" t="inlineStr">
+      <c r="P76" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q75" s="30" t="inlineStr">
+      <c r="Q76" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>4.156</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>4.967</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>3.067</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>4.431</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>7.792</v>
+        <v>4.156</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.967</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.067</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>3.45</v>
       </c>
       <c r="O77" s="32" t="n">
-        <v>10.8</v>
+        <v>4.133</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>8.467000000000001</v>
+        <v>4.431</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>0.896</v>
+        <v>7.792</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>1.25</v>
+        <v>9.25</v>
       </c>
       <c r="D78" s="32" t="inlineStr">
         <is>
@@ -3696,28 +3621,28 @@
         </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>2.6</v>
+        <v>10.8</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>1.444</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.021000000000001</v>
+        <v>0.896</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>9.25</v>
+        <v>1.25</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -3771,75 +3696,150 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.778</v>
+        <v>1.444</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>8.021000000000001</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>7.778</v>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B80" s="32" t="n">
+      <c r="B81" s="32" t="n">
         <v>0.459</v>
       </c>
-      <c r="C80" s="32" t="n">
+      <c r="C81" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="D80" s="32" t="n">
+      <c r="D81" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E80" s="32" t="n">
+      <c r="E81" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="F80" s="32" t="n">
+      <c r="F81" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G80" s="32" t="n">
+      <c r="G81" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H80" s="36" t="inlineStr">
+      <c r="H81" s="36" t="inlineStr">
         <is>
           <t>16th</t>
         </is>
       </c>
-      <c r="I80" s="32" t="inlineStr">
+      <c r="I81" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J80" s="36" t="inlineStr">
+      <c r="J81" s="36" t="inlineStr">
         <is>
           <t>20th</t>
         </is>
       </c>
-      <c r="K80" s="32" t="n">
+      <c r="K81" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L80" s="32" t="n">
+      <c r="L81" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M80" s="32" t="n">
+      <c r="M81" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="N80" s="32" t="n">
+      <c r="N81" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="O80" s="32" t="n">
+      <c r="O81" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="P80" s="32" t="n">
+      <c r="P81" s="32" t="n">
         <v>0.486</v>
       </c>
-      <c r="Q80" s="35" t="inlineStr">
+      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4774,7 +4774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4791,320 +4791,170 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Los Angeles Angels offense vs Seattle Mariners defense</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E67" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F67" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G67" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H67" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I67" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J67" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K67" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L67" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M67" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N67" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O67" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P67" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q67" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>4.653</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>5.233</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H68" s="34" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>4.233</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>4.105</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>7.714</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>7.979</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>1.184</v>
+        <v>4.653</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.233</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>23rd</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>4.55</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>1</v>
+        <v>4.233</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>0.958</v>
+        <v>4.105</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>9.286</v>
+        <v>7.714</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -5158,394 +5008,394 @@
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>8.333</v>
+        <v>7.979</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>9.286</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.595</v>
       </c>
-      <c r="C72" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D72" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E72" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="F72" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G72" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H72" s="34" t="inlineStr">
+      <c r="H74" s="34" t="inlineStr">
         <is>
           <t>22nd</t>
         </is>
       </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="36" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="36" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="K72" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L72" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M72" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="N72" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="O72" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P72" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.425</v>
       </c>
-      <c r="Q72" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Seattle Mariners offense vs Los Angeles Angels defense</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D75" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E75" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F75" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G75" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H75" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I75" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J75" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K75" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L75" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M75" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N75" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O75" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P75" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q75" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>3.067</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H76" s="36" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J76" s="36" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>5.147</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>7.854</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>8.244999999999999</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>1.312</v>
+        <v>3.93</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3.867</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>3.067</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J78" s="36" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>4.45</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>2</v>
+        <v>4.867</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>1.061</v>
+        <v>5.147</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.646000000000001</v>
+        <v>7.854</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -5599,71 +5449,221 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.816000000000001</v>
+        <v>8.244999999999999</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>8.646000000000001</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>8.816000000000001</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B80" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.479</v>
       </c>
-      <c r="C80" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="D80" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="E80" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F80" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="G80" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="34" t="inlineStr">
+      <c r="H82" s="34" t="inlineStr">
         <is>
           <t>28th</t>
         </is>
       </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="33" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="33" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="K80" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L80" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M80" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="N80" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="O80" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="P80" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.5679999999999999</v>
       </c>
-      <c r="Q80" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5682,7 +5682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5699,245 +5699,170 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>San Diego Padres offense vs Los Angeles Dodgers defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>4.013</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>3.967</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>3.487</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.087</v>
+        <v>4.013</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>3.967</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>4.5</v>
       </c>
       <c r="O71" s="32" t="n">
-        <v>6.75</v>
+        <v>4.167</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>6.596</v>
+        <v>3.487</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.022</v>
+        <v>7.087</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>1.5</v>
+        <v>7.25</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -5991,28 +5916,28 @@
         </is>
       </c>
       <c r="O72" s="32" t="n">
-        <v>1.75</v>
+        <v>6.75</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>0.83</v>
+        <v>6.596</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.348000000000001</v>
+        <v>1.022</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="D73" s="32" t="inlineStr">
         <is>
@@ -6066,319 +5991,319 @@
         </is>
       </c>
       <c r="O73" s="32" t="n">
-        <v>7.75</v>
+        <v>1.75</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>8.106</v>
+        <v>0.83</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8.348000000000001</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>8.106</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="C74" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="D74" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="E74" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="F74" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="G74" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H74" s="34" t="inlineStr">
+      <c r="H75" s="34" t="inlineStr">
         <is>
           <t>25th</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.452</v>
       </c>
-      <c r="Q74" s="35" t="inlineStr">
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Los Angeles Dodgers offense vs San Diego Padres defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>5.474</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>4.177</v>
-      </c>
-      <c r="Q78" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>9.191000000000001</v>
+        <v>5.474</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.333</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>5.4</v>
       </c>
       <c r="O79" s="32" t="n">
-        <v>8.75</v>
+        <v>5.133</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.848</v>
+        <v>4.177</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>1.553</v>
+        <v>9.191000000000001</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -6432,28 +6357,28 @@
         </is>
       </c>
       <c r="O80" s="32" t="n">
-        <v>1.5</v>
+        <v>8.75</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>0.848</v>
+        <v>7.848</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8.510999999999999</v>
+        <v>1.553</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>7.75</v>
+        <v>1</v>
       </c>
       <c r="D81" s="32" t="inlineStr">
         <is>
@@ -6507,75 +6432,150 @@
         </is>
       </c>
       <c r="O81" s="32" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.304</v>
+        <v>0.848</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>8.510999999999999</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>8.304</v>
+      </c>
+      <c r="Q82" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.658</v>
       </c>
-      <c r="C82" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="D82" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="E82" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="F82" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G82" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H82" s="36" t="inlineStr">
+      <c r="H83" s="36" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="I82" s="32" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="J82" s="34" t="inlineStr">
+      <c r="J83" s="34" t="inlineStr">
         <is>
           <t>26th</t>
         </is>
       </c>
-      <c r="K82" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="L82" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M82" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="N82" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="O82" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="P82" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q82" s="35" t="inlineStr">
+      <c r="Q83" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6816,13 +6816,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6907364341085271</v>
+        <v>0.6982509505703423</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-223</v>
+        <v>-231</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 69.1% (fair -223). Your call.</t>
+          <t>Model 69.8% (fair -231). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -6882,7 +6882,7 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.650148148148148</v>
+        <v>0.6498888888888888</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-186</v>
@@ -6948,7 +6948,7 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6491851851851852</v>
+        <v>0.6487407407407407</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-185</v>
@@ -7014,13 +7014,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5663565891472868</v>
+        <v>0.5663529411764706</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>-131</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7080,10 +7080,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6143612334801762</v>
+        <v>0.618193832599119</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-159</v>
+        <v>-162</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>127</v>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5694222222222223</v>
+        <v>0.5747111111111111</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-132</v>
+        <v>-135</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>125</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -7188,37 +7188,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ Seattle Mariners</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5818137254901961</v>
+        <v>0.3822789115646258</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-139</v>
+        <v>162</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -7254,37 +7254,37 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.3843877551020409</v>
+        <v>0.56005</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>160</v>
+        <v>-127</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -7308,7 +7308,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +160). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -7344,13 +7344,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.3995390070921985</v>
+        <v>0.4023381294964029</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -7391,32 +7391,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ Arizona Diamondbacks</t>
+          <t>Minnesota Twins @ New York Yankees</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5444117647058824</v>
+        <v>0.3985971223021583</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-119</v>
+        <v>151</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -7457,32 +7457,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ New York Yankees</t>
+          <t>St. Louis Cardinals @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3973741007194244</v>
+        <v>0.4336470588235294</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -7518,37 +7518,37 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Baltimore Orioles @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies -1.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4313438735177865</v>
+        <v>0.5670519230769231</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>132</v>
+        <v>-131</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>153</v>
+        <v>-108</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -7584,37 +7584,37 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5396</v>
+        <v>0.5215384615384615</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-117</v>
+        <v>-109</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -7655,32 +7655,32 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4971889400921659</v>
+        <v>0.529656862745098</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>101</v>
+        <v>-113</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Cincinnati Reds</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -7736,17 +7736,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5712070422535211</v>
+        <v>0.4971889400921659</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-133</v>
+        <v>101</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-113</v>
+        <v>117</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -7806,13 +7806,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4660869565217392</v>
+        <v>0.461931330472103</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -7853,32 +7853,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Pittsburgh Pirates @ Washington Nationals</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5477926829268294</v>
+        <v>0.4885454545454545</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-121</v>
+        <v>105</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-105</v>
+        <v>120</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -7914,37 +7914,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Colorado Rockies</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4165625</v>
+        <v>0.5829272727272726</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>140</v>
+        <v>-140</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>156</v>
+        <v>-120</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -7980,17 +7980,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>San Francisco Giants @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -8000,17 +8000,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.53245</v>
+        <v>0.41640625</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-114</v>
+        <v>140</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8046,37 +8046,37 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Washington Nationals</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4944186046511628</v>
+        <v>0.4171146245059288</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -8127,22 +8127,22 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4336326530612244</v>
+        <v>0.5514666666666667</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>131</v>
+        <v>-123</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>145</v>
+        <v>-110</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -8178,12 +8178,12 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Athletics</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -8193,22 +8193,22 @@
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Los Angeles Angels +1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5351411764705882</v>
+        <v>0.565374193548387</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-115</v>
+        <v>-130</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-104</v>
+        <v>-117</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -8244,12 +8244,12 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Miami Marlins @ Athletics</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -8259,22 +8259,22 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels +1.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5647220183486238</v>
+        <v>0.5232</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-130</v>
+        <v>-110</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-118</v>
+        <v>100</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -8315,12 +8315,12 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -8330,17 +8330,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>Texas Rangers -1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5686363636363636</v>
+        <v>0.3501013513513513</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-132</v>
+        <v>186</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-120</v>
+        <v>196</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 35.0% (fair +186). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -8376,17 +8376,17 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Chicago Cubs</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -8396,17 +8396,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5410384615384616</v>
+        <v>0.673437062937063</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-118</v>
+        <v>-206</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-108</v>
+        <v>-186</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -8430,7 +8430,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 67.3% (fair -206). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -8463,7 +8463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P118"/>
+  <dimension ref="A1:P120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4490090090090091</v>
+        <v>0.4541441441441442</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>122</v>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5509783783783784</v>
+        <v>0.5458675675675675</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-123</v>
+        <v>-120</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-122</v>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.588</v>
+        <v>0.5818</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-143</v>
+        <v>-139</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>113</v>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.412</v>
+        <v>0.4182</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>110</v>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8871,10 +8871,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4313438735177865</v>
+        <v>0.4171146245059288</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>153</v>
@@ -8901,7 +8901,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8937,10 +8937,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5686363636363636</v>
+        <v>0.5829272727272726</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-132</v>
+        <v>-140</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>-120</v>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3265384615384615</v>
+        <v>0.3265734265734265</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>206</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5447</v>
+        <v>0.5507</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-120</v>
+        <v>-123</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>107</v>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4553</v>
+        <v>0.4493</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>120</v>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5694222222222223</v>
+        <v>0.5747111111111111</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-132</v>
+        <v>-135</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>125</v>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9333,10 +9333,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4306194690265487</v>
+        <v>0.4253097345132744</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>126</v>
@@ -9363,7 +9363,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9399,7 +9399,7 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5497925110132159</v>
+        <v>0.5498484581497798</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>-122</v>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4502202643171806</v>
+        <v>0.4501321585903084</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>122</v>
@@ -9531,10 +9531,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.42</v>
+        <v>0.4172</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>111</v>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9597,10 +9597,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5800000000000001</v>
+        <v>0.5828</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-138</v>
+        <v>-140</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>105</v>
@@ -9627,7 +9627,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9663,13 +9663,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.53245</v>
+        <v>0.5215384615384615</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-114</v>
+        <v>-109</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9729,13 +9729,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4675336633663366</v>
+        <v>0.4784192307692308</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-102</v>
+        <v>-108</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9791,17 +9791,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5034975369458128</v>
+        <v>0.4173</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-101</v>
+        <v>140</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9857,14 +9857,14 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4965</v>
+        <v>0.5827</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>101</v>
+        <v>-140</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>100</v>
@@ -9891,7 +9891,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +101). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9927,13 +9927,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4948557692307692</v>
+        <v>0.495</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>102</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9993,13 +9993,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5051466019417475</v>
+        <v>0.5050038461538461</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>-102</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-106</v>
+        <v>-108</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10059,13 +10059,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4072</v>
+        <v>0.3987</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>106</v>
+        <v>-105</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5928</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-146</v>
+        <v>-151</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>117</v>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10191,7 +10191,7 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.3508148148148148</v>
+        <v>0.3512592592592593</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>185</v>
@@ -10257,7 +10257,7 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.6491851851851852</v>
+        <v>0.6487407407407407</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>-185</v>
@@ -10323,10 +10323,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5293036866359447</v>
+        <v>0.5300046082949309</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>-117</v>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -10389,10 +10389,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4707339449541285</v>
+        <v>0.47</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>118</v>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5201</v>
+        <v>0.5133</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>113</v>
@@ -10485,7 +10485,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -10521,13 +10521,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4799</v>
+        <v>0.4867</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -10587,13 +10587,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.50415</v>
+        <v>0.5074752475247524</v>
       </c>
       <c r="G35" s="14" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H35" s="15" t="n">
         <v>-102</v>
-      </c>
-      <c r="H35" s="15" t="n">
-        <v>100</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -10653,13 +10653,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.4958108910891089</v>
+        <v>0.4925</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -10683,7 +10683,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -10719,13 +10719,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5887</v>
+        <v>0.6455</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-143</v>
+        <v>-182</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 64.5% (fair -182). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -10785,13 +10785,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4113</v>
+        <v>0.3545</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 35.5% (fair +182). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.3498648648648649</v>
+        <v>0.3501013513513513</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>186</v>
@@ -10917,7 +10917,7 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.650148148148148</v>
+        <v>0.6498888888888888</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>-186</v>
@@ -10983,10 +10983,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.3843877551020409</v>
+        <v>0.3822789115646258</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>194</v>
@@ -11013,7 +11013,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +160). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -11049,13 +11049,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.6155870748299319</v>
+        <v>0.6176986622073579</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-160</v>
+        <v>-162</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-194</v>
+        <v>-199</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -160). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -11115,10 +11115,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.495</v>
+        <v>0.4739</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>115</v>
@@ -11145,7 +11145,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -11181,10 +11181,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5261</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-102</v>
+        <v>-111</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>114</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -11247,7 +11247,7 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4352558139534884</v>
+        <v>0.4346046511627907</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>130</v>
@@ -11313,13 +11313,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5647220183486238</v>
+        <v>0.565374193548387</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>-130</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-118</v>
+        <v>-117</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -11379,13 +11379,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.3995390070921985</v>
+        <v>0.4023381294964029</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -11445,10 +11445,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.6004709219858156</v>
+        <v>0.5976312056737588</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-150</v>
+        <v>-149</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>-182</v>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -11511,10 +11511,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4602</v>
+        <v>0.4477</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>113</v>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -11577,13 +11577,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5398000000000001</v>
+        <v>0.5523</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-117</v>
+        <v>-123</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -11607,7 +11607,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.3856338028169015</v>
+        <v>0.3817840375586855</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>113</v>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -11709,10 +11709,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.6143612334801762</v>
+        <v>0.618193832599119</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-159</v>
+        <v>-162</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>127</v>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -11775,13 +11775,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4589671361502348</v>
+        <v>0.4467741935483871</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -11841,13 +11841,13 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5410384615384616</v>
+        <v>0.5532315315315315</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-118</v>
+        <v>-124</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-108</v>
+        <v>-122</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -11907,10 +11907,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4522058823529412</v>
+        <v>0.448578431372549</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>104</v>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -11973,13 +11973,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5477926829268294</v>
+        <v>0.5514666666666667</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-121</v>
+        <v>-123</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -12039,13 +12039,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4336326530612244</v>
+        <v>0.4336470588235294</v>
       </c>
       <c r="G57" s="14" t="n">
         <v>131</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -12105,13 +12105,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5663565891472868</v>
+        <v>0.5663529411764706</v>
       </c>
       <c r="G58" s="14" t="n">
         <v>-131</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -12171,13 +12171,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4944186046511628</v>
+        <v>0.4885454545454545</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -12201,7 +12201,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -12237,13 +12237,13 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5055818181818181</v>
+        <v>0.5114657657657657</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-102</v>
+        <v>-105</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.5052666666666666</v>
+        <v>0.5045529411764705</v>
       </c>
       <c r="G61" s="14" t="n">
         <v>-102</v>
@@ -12369,7 +12369,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.494713725490196</v>
+        <v>0.4954274509803921</v>
       </c>
       <c r="G62" s="14" t="n">
         <v>102</v>
@@ -12435,13 +12435,13 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.3694509803921569</v>
+        <v>0.364921875</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -12465,7 +12465,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 36.5% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -12501,13 +12501,13 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.63058125</v>
+        <v>0.6350802281368821</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-171</v>
+        <v>-174</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -12531,7 +12531,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 63.5% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.3973741007194244</v>
+        <v>0.3985971223021583</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H65" s="15" t="n">
         <v>178</v>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -12633,13 +12633,13 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.6026388489208633</v>
+        <v>0.6013795620437956</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-152</v>
+        <v>-151</v>
       </c>
       <c r="H66" s="15" t="n">
-        <v>-178</v>
+        <v>-174</v>
       </c>
       <c r="I66" s="13">
         <f>IF($H$66="","",IF($H$66&lt;0,-$H$66/(-$H$66+100),100/($H$66+100)))</f>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 60.3% (fair -152). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -12699,13 +12699,13 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.4942038461538461</v>
+        <v>0.4928821782178218</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H67" s="15" t="n">
-        <v>-108</v>
+        <v>-102</v>
       </c>
       <c r="I67" s="13">
         <f>IF($H$67="","",IF($H$67&lt;0,-$H$67/(-$H$67+100),100/($H$67+100)))</f>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -12765,13 +12765,13 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5058</v>
+        <v>0.5071078431372549</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="H68" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I68" s="13">
         <f>IF($H$68="","",IF($H$68&lt;0,-$H$68/(-$H$68+100),100/($H$68+100)))</f>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -12831,13 +12831,13 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.436046511627907</v>
+        <v>0.4327064220183487</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H69" s="15" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -12897,13 +12897,13 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5639444444444444</v>
+        <v>0.5673039647577093</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-129</v>
+        <v>-131</v>
       </c>
       <c r="H70" s="15" t="n">
-        <v>-125</v>
+        <v>-127</v>
       </c>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -12963,13 +12963,13 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.5712070422535211</v>
+        <v>0.5670519230769231</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-133</v>
+        <v>-131</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -12993,7 +12993,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.4287980769230769</v>
+        <v>0.4329807692307692</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H72" s="15" t="n">
         <v>108</v>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -13095,13 +13095,13 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5305</v>
+        <v>0.4626</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-113</v>
+        <v>116</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -13161,13 +13161,13 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4695</v>
+        <v>0.5374</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>113</v>
+        <v>-116</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -13191,7 +13191,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.5339092436974789</v>
+        <v>0.5380840336134454</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="H75" s="15" t="n">
         <v>-138</v>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -13293,13 +13293,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.4660869565217392</v>
+        <v>0.461931330472103</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -13359,13 +13359,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4693548387096774</v>
+        <v>0.4670909090909091</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -13389,7 +13389,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -13425,10 +13425,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5306450450450451</v>
+        <v>0.5328981981981982</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>-122</v>
@@ -13455,7 +13455,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -13491,13 +13491,13 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5146470588235295</v>
+        <v>0.4891666666666666</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-106</v>
+        <v>104</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 48.9% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.485343137254902</v>
+        <v>0.5108235294117647</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>106</v>
+        <v>-104</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>104</v>
+        <v>-104</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -13587,7 +13587,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 51.1% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -13623,13 +13623,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.3754999999999999</v>
+        <v>0.370532319391635</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +166). Your call.</t>
+          <t>Model 37.1% (fair +170). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -13689,13 +13689,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.6245296296296295</v>
+        <v>0.6294669064748201</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-166</v>
+        <v>-170</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -13719,7 +13719,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -166). Your call.</t>
+          <t>Model 62.9% (fair -170). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -13887,10 +13887,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4603846153846154</v>
+        <v>0.439951923076923</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>108</v>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -13953,10 +13953,10 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5396</v>
+        <v>0.56005</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-117</v>
+        <v>-127</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>100</v>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -14019,13 +14019,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.3092692307692308</v>
+        <v>0.3017602996254682</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 30.9% (fair +223). Your call.</t>
+          <t>Model 30.2% (fair +231). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6907364341085271</v>
+        <v>0.6982509505703423</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-223</v>
+        <v>-231</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 69.1% (fair -223). Your call.</t>
+          <t>Model 69.8% (fair -231). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -14151,13 +14151,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5834765625</v>
+        <v>0.5836391634980989</v>
       </c>
       <c r="G89" s="14" t="n">
         <v>-140</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -14181,7 +14181,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -14217,7 +14217,7 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4165625</v>
+        <v>0.41640625</v>
       </c>
       <c r="G90" s="14" t="n">
         <v>140</v>
@@ -14247,7 +14247,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -14421,7 +14421,7 @@
         <v>104</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -14547,13 +14547,13 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.5158196078431372</v>
+        <v>0.5030392156862745</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-107</v>
+        <v>-101</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -14577,7 +14577,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -14613,13 +14613,13 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.4842156862745098</v>
+        <v>0.496956862745098</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>104</v>
+        <v>-104</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -14643,7 +14643,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -14679,13 +14679,13 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4551612903225807</v>
+        <v>0.4477727272727272</v>
       </c>
       <c r="G97" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="H97" s="15" t="n">
         <v>120</v>
-      </c>
-      <c r="H97" s="15" t="n">
-        <v>117</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -14709,7 +14709,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -14745,13 +14745,13 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.544831797235023</v>
+        <v>0.5522423423423423</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-120</v>
+        <v>-123</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>-117</v>
+        <v>-122</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -14775,7 +14775,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -14811,13 +14811,13 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.4648392156862745</v>
+        <v>0.4768</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -14841,7 +14841,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -14877,13 +14877,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.5351411764705882</v>
+        <v>0.5232</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -14907,7 +14907,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -14943,10 +14943,10 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.402</v>
+        <v>0.4042352941176471</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H101" s="15" t="n">
         <v>155</v>
@@ -14973,7 +14973,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 40.4% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -15009,10 +15009,10 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5980406250000001</v>
+        <v>0.5957859375</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-149</v>
+        <v>-147</v>
       </c>
       <c r="H102" s="15" t="n">
         <v>-156</v>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 59.6% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -15075,10 +15075,10 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.6686</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>-202</v>
+        <v>-201</v>
       </c>
       <c r="H103" s="15" t="n"/>
       <c r="I103" s="13">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 66.9% (fair -202). Your call.</t>
+          <t>Model 66.8% (fair -201). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -15139,10 +15139,10 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.3314</v>
+        <v>0.3322</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H104" s="15" t="n"/>
       <c r="I104" s="13">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 33.1% (fair +202). Your call.</t>
+          <t>Model 33.2% (fair +201). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -15199,17 +15199,17 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.4556</v>
+        <v>0.517725</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>119</v>
+        <v>-107</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>100</v>
+        <v>-108</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -15265,14 +15265,14 @@
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5444117647058824</v>
+        <v>0.4823039215686274</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-119</v>
+        <v>107</v>
       </c>
       <c r="H106" s="15" t="n">
         <v>104</v>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -15335,13 +15335,13 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.5139272727272727</v>
+        <v>0.5020807511737089</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>-106</v>
+        <v>-101</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>-120</v>
+        <v>-113</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -15401,13 +15401,13 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.4861057692307693</v>
+        <v>0.4979024390243902</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -15467,10 +15467,10 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.4052</v>
+        <v>0.4114</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H109" s="15" t="n"/>
       <c r="I109" s="13">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 41.1% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -15531,10 +15531,10 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.5948</v>
+        <v>0.5886</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>-147</v>
+        <v>-143</v>
       </c>
       <c r="H110" s="15" t="n"/>
       <c r="I110" s="13">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -15595,13 +15595,13 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.4449</v>
+        <v>0.4331</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -15625,7 +15625,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -15661,13 +15661,13 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.5550999999999999</v>
+        <v>0.5669</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>-125</v>
+        <v>-131</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -15727,10 +15727,10 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4799803921568627</v>
+        <v>0.4790117647058823</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H113" s="15" t="n">
         <v>-104</v>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -15793,13 +15793,13 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5200317073170733</v>
+        <v>0.5209686274509804</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -15823,7 +15823,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -15859,10 +15859,10 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.5289</v>
+        <v>0.5299</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="H115" s="15" t="n"/>
       <c r="I115" s="13">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -15923,10 +15923,10 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.4711</v>
+        <v>0.4701</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H116" s="15" t="n"/>
       <c r="I116" s="13">
@@ -15951,7 +15951,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -15983,17 +15983,17 @@
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.41815</v>
+        <v>0.4703465346534653</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -16049,14 +16049,14 @@
       </c>
       <c r="E118" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.5818137254901961</v>
+        <v>0.529656862745098</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>-139</v>
+        <v>-113</v>
       </c>
       <c r="H118" s="15" t="n">
         <v>104</v>
@@ -16083,7 +16083,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -16092,9 +16092,141 @@
         <v/>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Seattle Mariners +1.5</t>
+        </is>
+      </c>
+      <c r="F119" s="13" t="n">
+        <v>0.6108924812030075</v>
+      </c>
+      <c r="G119" s="14" t="n">
+        <v>-157</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>-166</v>
+      </c>
+      <c r="I119" s="13">
+        <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
+        <v/>
+      </c>
+      <c r="J119" s="16">
+        <f>IF($H$119="","",$F$119*IF($H$119&lt;0,-100/$H$119,$H$119/100)-(1-$F$119))</f>
+        <v/>
+      </c>
+      <c r="K119" s="17">
+        <f>IF($H$119="","",MAX(0,($F$119*IF($H$119&lt;0,-100/$H$119,$H$119/100)-(1-$F$119))/IF($H$119&lt;0,-100/$H$119,$H$119/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L119" s="18">
+        <f>IF($H$119="","",ROUND(MIN($K$119,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M119" s="12">
+        <f>IF($J$119="","",IF($J$119&lt;0,"Pass",IF($J$119&lt;'Settings'!$B$4,"Thin",IF($J$119&lt;0.06,"✅ Sharp band",IF($J$119&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N119" s="19" t="inlineStr">
+        <is>
+          <t>Model 61.1% (fair -157). Your call.</t>
+        </is>
+      </c>
+      <c r="O119" s="15" t="n"/>
+      <c r="P119" s="16">
+        <f>IF(OR($H$119="",$O$119=""),"",(1+IF($H$119&lt;0,-100/$H$119,$H$119/100))/(1+IF($O$119&lt;0,-100/$O$119,$O$119/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B120" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D120" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E120" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays -1.5</t>
+        </is>
+      </c>
+      <c r="F120" s="13" t="n">
+        <v>0.3890833333333333</v>
+      </c>
+      <c r="G120" s="14" t="n">
+        <v>157</v>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="I120" s="13">
+        <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
+        <v/>
+      </c>
+      <c r="J120" s="16">
+        <f>IF($H$120="","",$F$120*IF($H$120&lt;0,-100/$H$120,$H$120/100)-(1-$F$120))</f>
+        <v/>
+      </c>
+      <c r="K120" s="17">
+        <f>IF($H$120="","",MAX(0,($F$120*IF($H$120&lt;0,-100/$H$120,$H$120/100)-(1-$F$120))/IF($H$120&lt;0,-100/$H$120,$H$120/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L120" s="18">
+        <f>IF($H$120="","",ROUND(MIN($K$120,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M120" s="12">
+        <f>IF($J$120="","",IF($J$120&lt;0,"Pass",IF($J$120&lt;'Settings'!$B$4,"Thin",IF($J$120&lt;0.06,"✅ Sharp band",IF($J$120&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N120" s="19" t="inlineStr">
+        <is>
+          <t>Model 38.9% (fair +157). Your call.</t>
+        </is>
+      </c>
+      <c r="O120" s="15" t="n"/>
+      <c r="P120" s="16">
+        <f>IF(OR($H$120="",$O$120=""),"",(1+IF($H$120&lt;0,-100/$H$120,$H$120/100))/(1+IF($O$120&lt;0,-100/$O$120,$O$120/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J118">
+  <conditionalFormatting sqref="J5:J120">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -16198,28 +16330,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2501</v>
+        <v>0.2503</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.4545</v>
+        <v>0.4571</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-3.43</v>
+        <v>-2.16</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-1.64</v>
+        <v>-1.03</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5027</v>
+        <v>0.5054</v>
       </c>
     </row>
     <row r="6">
@@ -16229,28 +16361,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2517</v>
+        <v>0.2518</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.4706</v>
+        <v>0.4737</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>-0.77</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>-0.46</v>
+        <v>0.29</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>2.79</v>
+        <v>3.53</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5226</v>
+        <v>0.5256</v>
       </c>
     </row>
     <row r="7">
@@ -16333,7 +16465,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=264, ECE 0.055 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=265, ECE 0.057 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -16428,16 +16560,16 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.4578</v>
+        <v>0.4579</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.4634</v>
+        <v>0.4699</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>0.0056</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="21">
